--- a/roteiro original.xlsx
+++ b/roteiro original.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC 0025\Desktop\Estudo roteiro promotores  autoserviço\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A153BA95-CA59-48B4-98DC-CB9A48356A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4690AF-EA38-4A9B-8AF7-7A99C36674BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{18824AD4-335A-446D-A7D9-07F1443FEBAC}"/>
   </bookViews>
@@ -20,9 +20,10 @@
     <sheet name="rascunho" sheetId="3" r:id="rId5"/>
     <sheet name=" Simularção reduzir das redes " sheetId="9" r:id="rId6"/>
     <sheet name="Planilha4" sheetId="8" r:id="rId7"/>
+    <sheet name="Planilha1" sheetId="10" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">rascunho!$A$2:$P$76</definedName>
@@ -33,19 +34,19 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
-    <pivotCache cacheId="1" r:id="rId10"/>
+    <pivotCache cacheId="3" r:id="rId10"/>
+    <pivotCache cacheId="4" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="2" r:id="rId11"/>
+        <pivotCache cacheId="5" r:id="rId12"/>
       </x14:pivotCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId12"/>
         <x14:slicerCache r:id="rId13"/>
+        <x14:slicerCache r:id="rId14"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -89,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="419">
   <si>
     <t>Av. Godofredo Maciel, 2540</t>
   </si>
@@ -1304,6 +1305,48 @@
   </si>
   <si>
     <t>Joao makson Oliveira</t>
+  </si>
+  <si>
+    <t>Cometa</t>
+  </si>
+  <si>
+    <t>Rede</t>
+  </si>
+  <si>
+    <t>Terça</t>
+  </si>
+  <si>
+    <t>Centerbox</t>
+  </si>
+  <si>
+    <t>GPA</t>
+  </si>
+  <si>
+    <t>Quinta</t>
+  </si>
+  <si>
+    <t>Frangolandia</t>
+  </si>
+  <si>
+    <t>Super do Povo</t>
+  </si>
+  <si>
+    <t>Super lagoa</t>
+  </si>
+  <si>
+    <t>VISITAM TODAS AS LOJAS ATÉ? No roteiro atual</t>
+  </si>
+  <si>
+    <t>Pinheiro</t>
+  </si>
+  <si>
+    <t>Sexta (1 loja com visita na sexta) (Super do povo -Mini market)</t>
+  </si>
+  <si>
+    <t>Sexta (1 loja com visita na sexta) (Super Lagoa - Noth Shopping)</t>
+  </si>
+  <si>
+    <t>Sabado ( 3 lojas com visitas no sabado ) ( Pinheiro-Praia de Iracema , Cambeba , Rogaciano Leite)</t>
   </si>
 </sst>
 </file>
@@ -1575,7 +1618,43 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1597,42 +1676,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4451,7 +4494,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E699402A-8A71-4420-95C9-3464F8567244}" name="Tabela dinâmica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E699402A-8A71-4420-95C9-3464F8567244}" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -4570,7 +4613,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{60B45C95-8E4E-40AD-81AB-1B8E28A41E2F}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{60B45C95-8E4E-40AD-81AB-1B8E28A41E2F}" name="Tabela dinâmica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B102" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -6700,41 +6743,39 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="40">
-        <v>10931</v>
+        <v>12076</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="C6" s="40">
-        <v>9345</v>
+        <v>838</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>257</v>
+        <v>347</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>9</v>
+        <v>206</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="40">
-        <v>1</v>
-      </c>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40">
-        <v>1</v>
-      </c>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40">
-        <v>1</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40">
+        <v>1</v>
+      </c>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40">
+        <v>1</v>
+      </c>
+      <c r="K6" s="40"/>
       <c r="L6" s="40"/>
       <c r="M6" s="40">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f>SUM(G6:L6)</f>
+        <v>2</v>
       </c>
       <c r="N6" s="40">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
@@ -6769,7 +6810,7 @@
       </c>
       <c r="L7" s="40"/>
       <c r="M7" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G7:L7)</f>
         <v>3</v>
       </c>
       <c r="N7" s="40">
@@ -6806,7 +6847,7 @@
       </c>
       <c r="L8" s="26"/>
       <c r="M8" s="26">
-        <f t="shared" si="1"/>
+        <f>SUM(G8:L8)</f>
         <v>2</v>
       </c>
       <c r="N8" s="26">
@@ -6824,22 +6865,22 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="40">
-        <v>10931</v>
+        <v>12076</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="C9" s="40">
-        <v>337</v>
+        <v>11775</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>260</v>
+        <v>355</v>
       </c>
       <c r="E9" s="40" t="s">
-        <v>14</v>
+        <v>215</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G9" s="40"/>
       <c r="H9" s="40">
@@ -6852,31 +6893,31 @@
       <c r="K9" s="40"/>
       <c r="L9" s="40"/>
       <c r="M9" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G9:L9)</f>
         <v>2</v>
       </c>
       <c r="N9" s="40">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="40">
-        <v>10931</v>
+        <v>11023</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C10" s="40">
-        <v>9622</v>
+        <v>9340</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E10" s="40" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="G10" s="40"/>
       <c r="H10" s="40">
@@ -6891,48 +6932,50 @@
         <v>1</v>
       </c>
       <c r="M10" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G10:L10)</f>
         <v>3</v>
       </c>
       <c r="N10" s="40">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="40">
-        <v>10931</v>
+        <v>11678</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="C11" s="40">
-        <v>11809</v>
+        <v>989</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40">
-        <v>1</v>
-      </c>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40">
-        <v>1</v>
-      </c>
-      <c r="K11" s="40"/>
+        <v>99</v>
+      </c>
+      <c r="G11" s="40">
+        <v>1</v>
+      </c>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40">
+        <v>1</v>
+      </c>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40">
+        <v>1</v>
+      </c>
       <c r="L11" s="40"/>
       <c r="M11" s="40">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>SUM(G11:L11)</f>
+        <v>3</v>
       </c>
       <c r="N11" s="40">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -6967,7 +7010,7 @@
       </c>
       <c r="L12" s="26"/>
       <c r="M12" s="26">
-        <f t="shared" si="1"/>
+        <f>SUM(G12:L12)</f>
         <v>3</v>
       </c>
       <c r="N12" s="26">
@@ -7004,7 +7047,7 @@
       <c r="K13" s="40"/>
       <c r="L13" s="40"/>
       <c r="M13" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G13:L13)</f>
         <v>2</v>
       </c>
       <c r="N13" s="40">
@@ -7041,7 +7084,7 @@
       <c r="K14" s="40"/>
       <c r="L14" s="40"/>
       <c r="M14" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G14:L14)</f>
         <v>2</v>
       </c>
       <c r="N14" s="40">
@@ -7050,41 +7093,39 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
-        <v>11587</v>
+        <v>11932</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>24</v>
+        <v>130</v>
       </c>
       <c r="C15" s="40">
-        <v>1034</v>
+        <v>10946</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>266</v>
+        <v>311</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F15" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="40">
-        <v>1</v>
-      </c>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40">
-        <v>1</v>
-      </c>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40">
-        <v>1</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40">
+        <v>1</v>
+      </c>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40">
+        <v>1</v>
+      </c>
+      <c r="K15" s="40"/>
       <c r="L15" s="40"/>
       <c r="M15" s="40">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f>SUM(G15:L15)</f>
+        <v>2</v>
       </c>
       <c r="N15" s="40">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
@@ -7125,7 +7166,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G16:L16)</f>
         <v>6</v>
       </c>
       <c r="N16" s="40">
@@ -7164,7 +7205,7 @@
       </c>
       <c r="L17" s="40"/>
       <c r="M17" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G17:L17)</f>
         <v>3</v>
       </c>
       <c r="N17" s="40">
@@ -7173,22 +7214,22 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
-        <v>11023</v>
+        <v>12028</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="C18" s="40">
-        <v>9340</v>
+        <v>9346</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>269</v>
+        <v>324</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>39</v>
+        <v>164</v>
       </c>
       <c r="F18" s="40" t="s">
-        <v>40</v>
+        <v>165</v>
       </c>
       <c r="G18" s="40"/>
       <c r="H18" s="40">
@@ -7199,15 +7240,13 @@
         <v>1</v>
       </c>
       <c r="K18" s="40"/>
-      <c r="L18" s="40">
-        <v>1</v>
-      </c>
+      <c r="L18" s="40"/>
       <c r="M18" s="40">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f>SUM(G18:L18)</f>
+        <v>2</v>
       </c>
       <c r="N18" s="40">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -7240,7 +7279,7 @@
       <c r="K19" s="40"/>
       <c r="L19" s="40"/>
       <c r="M19" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G19:L19)</f>
         <v>2</v>
       </c>
       <c r="N19" s="40">
@@ -7249,22 +7288,22 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
-        <v>11023</v>
+        <v>12079</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>36</v>
+        <v>403</v>
       </c>
       <c r="C20" s="40">
-        <v>4393</v>
+        <v>4522</v>
       </c>
       <c r="D20" s="40" t="s">
-        <v>271</v>
+        <v>344</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="F20" s="40" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="G20" s="40"/>
       <c r="H20" s="40">
@@ -7275,13 +7314,15 @@
         <v>1</v>
       </c>
       <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
+      <c r="L20" s="40">
+        <v>1</v>
+      </c>
       <c r="M20" s="40">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>SUM(G20:L20)</f>
+        <v>3</v>
       </c>
       <c r="N20" s="40">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -7314,7 +7355,7 @@
       <c r="K21" s="26"/>
       <c r="L21" s="26"/>
       <c r="M21" s="26">
-        <f t="shared" si="1"/>
+        <f>SUM(G21:L21)</f>
         <v>2</v>
       </c>
       <c r="N21" s="26">
@@ -7353,7 +7394,7 @@
       </c>
       <c r="L22" s="40"/>
       <c r="M22" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G22:L22)</f>
         <v>3</v>
       </c>
       <c r="N22" s="40">
@@ -7388,7 +7429,7 @@
       <c r="K23" s="26"/>
       <c r="L23" s="26"/>
       <c r="M23" s="26">
-        <f t="shared" si="1"/>
+        <f>SUM(G23:L23)</f>
         <v>1</v>
       </c>
       <c r="N23" s="26">
@@ -7397,22 +7438,22 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
-        <v>11023</v>
+        <v>12027</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>36</v>
+        <v>404</v>
       </c>
       <c r="C24" s="40">
-        <v>4029</v>
+        <v>9347</v>
       </c>
       <c r="D24" s="40" t="s">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>47</v>
+        <v>172</v>
       </c>
       <c r="F24" s="40" t="s">
-        <v>40</v>
+        <v>173</v>
       </c>
       <c r="G24" s="40">
         <v>1</v>
@@ -7427,7 +7468,7 @@
       </c>
       <c r="L24" s="40"/>
       <c r="M24" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G24:L24)</f>
         <v>3</v>
       </c>
       <c r="N24" s="40">
@@ -7462,7 +7503,7 @@
       <c r="K25" s="26"/>
       <c r="L25" s="26"/>
       <c r="M25" s="26">
-        <f t="shared" si="1"/>
+        <f>SUM(G25:L25)</f>
         <v>1</v>
       </c>
       <c r="N25" s="26">
@@ -7497,7 +7538,7 @@
       </c>
       <c r="L26" s="40"/>
       <c r="M26" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G26:L26)</f>
         <v>1</v>
       </c>
       <c r="N26" s="40">
@@ -7506,61 +7547,61 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
-        <v>11023</v>
+        <v>12076</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>36</v>
+        <v>205</v>
       </c>
       <c r="C27" s="40">
-        <v>1058</v>
+        <v>9341</v>
       </c>
       <c r="D27" s="40" t="s">
-        <v>278</v>
+        <v>349</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>52</v>
+        <v>209</v>
       </c>
       <c r="F27" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40">
-        <v>1</v>
-      </c>
-      <c r="I27" s="40"/>
-      <c r="J27" s="40">
-        <v>1</v>
-      </c>
-      <c r="K27" s="40"/>
-      <c r="L27" s="40">
-        <v>1</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="G27" s="40">
+        <v>1</v>
+      </c>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40">
+        <v>1</v>
+      </c>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40">
+        <v>1</v>
+      </c>
+      <c r="L27" s="40"/>
       <c r="M27" s="40">
-        <f t="shared" si="1"/>
+        <f>SUM(G27:L27)</f>
         <v>3</v>
       </c>
       <c r="N27" s="40">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
-        <v>11679</v>
+        <v>12087</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>87</v>
+        <v>233</v>
       </c>
       <c r="C28" s="40">
-        <v>10948</v>
+        <v>1006</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>279</v>
+        <v>373</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>88</v>
+        <v>235</v>
       </c>
       <c r="F28" s="40" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="G28" s="40">
         <v>1</v>
@@ -7575,11 +7616,11 @@
       </c>
       <c r="L28" s="40"/>
       <c r="M28" s="40">
-        <f t="shared" ref="M28:M71" si="2">SUM(G28:L28)</f>
+        <f>SUM(G28:L28)</f>
         <v>3</v>
       </c>
       <c r="N28" s="40">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -7614,7 +7655,7 @@
       </c>
       <c r="L29" s="26"/>
       <c r="M29" s="26">
-        <f t="shared" si="2"/>
+        <f>SUM(G29:L29)</f>
         <v>3</v>
       </c>
       <c r="N29" s="26">
@@ -7651,7 +7692,7 @@
       <c r="K30" s="40"/>
       <c r="L30" s="40"/>
       <c r="M30" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G30:L30)</f>
         <v>2</v>
       </c>
       <c r="N30" s="40">
@@ -7660,36 +7701,38 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
-        <v>11679</v>
+        <v>12155</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>87</v>
+        <v>244</v>
       </c>
       <c r="C31" s="40">
-        <v>1011</v>
+        <v>976</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>282</v>
+        <v>384</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>92</v>
+        <v>249</v>
       </c>
       <c r="F31" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40">
-        <v>1</v>
-      </c>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40">
-        <v>1</v>
-      </c>
-      <c r="K31" s="40"/>
+        <v>248</v>
+      </c>
+      <c r="G31" s="40">
+        <v>1</v>
+      </c>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40">
+        <v>1</v>
+      </c>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40">
+        <v>1</v>
+      </c>
       <c r="L31" s="40"/>
       <c r="M31" s="40">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f>SUM(G31:L31)</f>
+        <v>3</v>
       </c>
       <c r="N31" s="40">
         <v>35</v>
@@ -7733,7 +7776,7 @@
         <v>1</v>
       </c>
       <c r="M32" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G32:L32)</f>
         <v>6</v>
       </c>
       <c r="N32" s="40">
@@ -7772,7 +7815,7 @@
       </c>
       <c r="L33" s="40"/>
       <c r="M33" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G33:L33)</f>
         <v>3</v>
       </c>
       <c r="N33" s="40">
@@ -7811,7 +7854,7 @@
       </c>
       <c r="L34" s="40"/>
       <c r="M34" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G34:L34)</f>
         <v>3</v>
       </c>
       <c r="N34" s="40">
@@ -7850,7 +7893,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G35:L35)</f>
         <v>3</v>
       </c>
       <c r="N35" s="40">
@@ -7889,7 +7932,7 @@
         <v>1</v>
       </c>
       <c r="M36" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G36:L36)</f>
         <v>3</v>
       </c>
       <c r="N36" s="40">
@@ -7898,22 +7941,22 @@
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
-        <v>11678</v>
+        <v>12076</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>95</v>
+        <v>205</v>
       </c>
       <c r="C37" s="40">
-        <v>989</v>
+        <v>942</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>288</v>
+        <v>354</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>101</v>
+        <v>214</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G37" s="40">
         <v>1</v>
@@ -7926,13 +7969,15 @@
       <c r="K37" s="40">
         <v>1</v>
       </c>
-      <c r="L37" s="40"/>
+      <c r="L37" s="40">
+        <v>1</v>
+      </c>
       <c r="M37" s="40">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f>SUM(G37:L37)</f>
+        <v>4</v>
       </c>
       <c r="N37" s="40">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
@@ -7965,7 +8010,7 @@
       <c r="K38" s="40"/>
       <c r="L38" s="40"/>
       <c r="M38" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G38:L38)</f>
         <v>2</v>
       </c>
       <c r="N38" s="40">
@@ -8002,7 +8047,7 @@
       <c r="K39" s="26"/>
       <c r="L39" s="26"/>
       <c r="M39" s="26">
-        <f t="shared" si="2"/>
+        <f>SUM(G39:L39)</f>
         <v>2</v>
       </c>
       <c r="N39" s="26">
@@ -8020,41 +8065,41 @@
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
-        <v>11678</v>
+        <v>11932</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="C40" s="40">
-        <v>950</v>
+        <v>967</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="F40" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40">
-        <v>1</v>
-      </c>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40">
-        <v>1</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G40" s="40">
+        <v>1</v>
+      </c>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40">
+        <v>1</v>
+      </c>
+      <c r="J40" s="40"/>
       <c r="K40" s="40">
         <v>1</v>
       </c>
       <c r="L40" s="40"/>
       <c r="M40" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G40:L40)</f>
         <v>3</v>
       </c>
       <c r="N40" s="40">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:23" s="41" customFormat="1" x14ac:dyDescent="0.25">
@@ -8087,7 +8132,7 @@
       <c r="K41" s="26"/>
       <c r="L41" s="26"/>
       <c r="M41" s="26">
-        <f t="shared" si="2"/>
+        <f>SUM(G41:L41)</f>
         <v>2</v>
       </c>
       <c r="N41" s="26">
@@ -8135,7 +8180,7 @@
         <v>1</v>
       </c>
       <c r="M42" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G42:L42)</f>
         <v>3</v>
       </c>
       <c r="N42" s="40">
@@ -8172,7 +8217,7 @@
       <c r="K43" s="26"/>
       <c r="L43" s="26"/>
       <c r="M43" s="26">
-        <f t="shared" si="2"/>
+        <f>SUM(G43:L43)</f>
         <v>2</v>
       </c>
       <c r="N43" s="26">
@@ -8218,7 +8263,7 @@
       <c r="K44" s="40"/>
       <c r="L44" s="40"/>
       <c r="M44" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G44:L44)</f>
         <v>2</v>
       </c>
       <c r="N44" s="40">
@@ -8257,7 +8302,7 @@
       </c>
       <c r="L45" s="40"/>
       <c r="M45" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G45:L45)</f>
         <v>3</v>
       </c>
       <c r="N45" s="40">
@@ -8296,7 +8341,7 @@
       </c>
       <c r="L46" s="40"/>
       <c r="M46" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G46:L46)</f>
         <v>3</v>
       </c>
       <c r="N46" s="40">
@@ -8335,7 +8380,7 @@
         <v>1</v>
       </c>
       <c r="M47" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G47:L47)</f>
         <v>3</v>
       </c>
       <c r="N47" s="40">
@@ -8344,22 +8389,22 @@
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
-        <v>11868</v>
+        <v>11932</v>
       </c>
       <c r="B48" s="40" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C48" s="40">
-        <v>874</v>
+        <v>9339</v>
       </c>
       <c r="D48" s="40" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F48" s="40" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="G48" s="40">
         <v>1</v>
@@ -8374,11 +8419,11 @@
       </c>
       <c r="L48" s="40"/>
       <c r="M48" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G48:L48)</f>
         <v>3</v>
       </c>
       <c r="N48" s="40">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.25">
@@ -8389,13 +8434,13 @@
         <v>115</v>
       </c>
       <c r="C49" s="40">
-        <v>1043</v>
+        <v>874</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F49" s="40" t="s">
         <v>112</v>
@@ -8413,11 +8458,11 @@
       </c>
       <c r="L49" s="40"/>
       <c r="M49" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G49:L49)</f>
         <v>3</v>
       </c>
       <c r="N49" s="40">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:23" s="41" customFormat="1" x14ac:dyDescent="0.25">
@@ -8450,7 +8495,7 @@
       </c>
       <c r="L50" s="26"/>
       <c r="M50" s="26">
-        <f t="shared" si="2"/>
+        <f>SUM(G50:L50)</f>
         <v>2</v>
       </c>
       <c r="N50" s="26">
@@ -8468,22 +8513,22 @@
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="40">
-        <v>11868</v>
+        <v>10931</v>
       </c>
       <c r="B51" s="40" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="C51" s="40">
-        <v>9602</v>
+        <v>9622</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="F51" s="40" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="G51" s="40"/>
       <c r="H51" s="40">
@@ -8494,13 +8539,15 @@
         <v>1</v>
       </c>
       <c r="K51" s="40"/>
-      <c r="L51" s="40"/>
+      <c r="L51" s="40">
+        <v>1</v>
+      </c>
       <c r="M51" s="40">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f>SUM(G51:L51)</f>
+        <v>3</v>
       </c>
       <c r="N51" s="40">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.25">
@@ -8533,7 +8580,7 @@
       <c r="K52" s="26"/>
       <c r="L52" s="26"/>
       <c r="M52" s="26">
-        <f t="shared" si="2"/>
+        <f>SUM(G52:L52)</f>
         <v>2</v>
       </c>
       <c r="N52" s="26">
@@ -8542,41 +8589,39 @@
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" s="40">
-        <v>11932</v>
+        <v>10931</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="C53" s="40">
-        <v>958</v>
+        <v>11809</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="F53" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="G53" s="40">
-        <v>1</v>
-      </c>
-      <c r="H53" s="40"/>
-      <c r="I53" s="40">
-        <v>1</v>
-      </c>
-      <c r="J53" s="40"/>
-      <c r="K53" s="40">
-        <v>1</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G53" s="40"/>
+      <c r="H53" s="40">
+        <v>1</v>
+      </c>
+      <c r="I53" s="40"/>
+      <c r="J53" s="40">
+        <v>1</v>
+      </c>
+      <c r="K53" s="40"/>
       <c r="L53" s="40"/>
       <c r="M53" s="40">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f>SUM(G53:L53)</f>
+        <v>2</v>
       </c>
       <c r="N53" s="40">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:23" s="41" customFormat="1" x14ac:dyDescent="0.25">
@@ -8609,7 +8654,7 @@
       <c r="K54" s="26"/>
       <c r="L54" s="26"/>
       <c r="M54" s="26">
-        <f t="shared" si="2"/>
+        <f>SUM(G54:L54)</f>
         <v>2</v>
       </c>
       <c r="N54" s="26">
@@ -8627,80 +8672,76 @@
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" s="40">
-        <v>11932</v>
+        <v>12087</v>
       </c>
       <c r="B55" s="40" t="s">
-        <v>130</v>
+        <v>233</v>
       </c>
       <c r="C55" s="40">
-        <v>967</v>
+        <v>954</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>306</v>
+        <v>377</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>134</v>
+        <v>239</v>
       </c>
       <c r="F55" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="G55" s="40">
-        <v>1</v>
-      </c>
-      <c r="H55" s="40"/>
-      <c r="I55" s="40">
-        <v>1</v>
-      </c>
-      <c r="J55" s="40"/>
-      <c r="K55" s="40">
-        <v>1</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40">
+        <v>1</v>
+      </c>
+      <c r="I55" s="40"/>
+      <c r="J55" s="40">
+        <v>1</v>
+      </c>
+      <c r="K55" s="40"/>
       <c r="L55" s="40"/>
       <c r="M55" s="40">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f>SUM(G55:L55)</f>
+        <v>2</v>
       </c>
       <c r="N55" s="40">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" s="40">
-        <v>11932</v>
+        <v>12028</v>
       </c>
       <c r="B56" s="40" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C56" s="40">
-        <v>9339</v>
+        <v>1482</v>
       </c>
       <c r="D56" s="40" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="E56" s="40" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="G56" s="40">
-        <v>1</v>
-      </c>
-      <c r="H56" s="40"/>
-      <c r="I56" s="40">
-        <v>1</v>
-      </c>
-      <c r="J56" s="40"/>
-      <c r="K56" s="40">
-        <v>1</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="G56" s="40"/>
+      <c r="H56" s="40">
+        <v>1</v>
+      </c>
+      <c r="I56" s="40"/>
+      <c r="J56" s="40">
+        <v>1</v>
+      </c>
+      <c r="K56" s="40"/>
       <c r="L56" s="40"/>
       <c r="M56" s="40">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f>SUM(G56:L56)</f>
+        <v>2</v>
       </c>
       <c r="N56" s="40">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -8735,7 +8776,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="26">
-        <f t="shared" si="2"/>
+        <f>SUM(G57:L57)</f>
         <v>3</v>
       </c>
       <c r="N57" s="26">
@@ -8772,7 +8813,7 @@
       <c r="K58" s="26"/>
       <c r="L58" s="26"/>
       <c r="M58" s="26">
-        <f t="shared" si="2"/>
+        <f>SUM(G58:L58)</f>
         <v>2</v>
       </c>
       <c r="N58" s="26">
@@ -8807,7 +8848,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="26">
-        <f t="shared" si="2"/>
+        <f>SUM(G59:L59)</f>
         <v>1</v>
       </c>
       <c r="N59" s="26">
@@ -8816,39 +8857,41 @@
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="40">
-        <v>11932</v>
+        <v>11587</v>
       </c>
       <c r="B60" s="40" t="s">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="C60" s="40">
-        <v>10946</v>
+        <v>1034</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>311</v>
+        <v>266</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="F60" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="G60" s="40"/>
-      <c r="H60" s="40">
-        <v>1</v>
-      </c>
-      <c r="I60" s="40"/>
-      <c r="J60" s="40">
-        <v>1</v>
-      </c>
-      <c r="K60" s="40"/>
+        <v>33</v>
+      </c>
+      <c r="G60" s="40">
+        <v>1</v>
+      </c>
+      <c r="H60" s="40"/>
+      <c r="I60" s="40">
+        <v>1</v>
+      </c>
+      <c r="J60" s="40"/>
+      <c r="K60" s="40">
+        <v>1</v>
+      </c>
       <c r="L60" s="40"/>
       <c r="M60" s="40">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f>SUM(G60:L60)</f>
+        <v>3</v>
       </c>
       <c r="N60" s="40">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.25">
@@ -8881,7 +8924,7 @@
       <c r="K61" s="40"/>
       <c r="L61" s="40"/>
       <c r="M61" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G61:L61)</f>
         <v>2</v>
       </c>
       <c r="N61" s="40">
@@ -8920,7 +8963,7 @@
       </c>
       <c r="L62" s="40"/>
       <c r="M62" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G62:L62)</f>
         <v>3</v>
       </c>
       <c r="N62" s="40">
@@ -8957,7 +9000,7 @@
       <c r="K63" s="40"/>
       <c r="L63" s="40"/>
       <c r="M63" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G63:L63)</f>
         <v>2</v>
       </c>
       <c r="N63" s="40">
@@ -8996,7 +9039,7 @@
       </c>
       <c r="L64" s="40"/>
       <c r="M64" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G64:L64)</f>
         <v>3</v>
       </c>
       <c r="N64" s="40">
@@ -9041,7 +9084,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G65:L65)</f>
         <v>6</v>
       </c>
       <c r="N65" s="40">
@@ -9076,7 +9119,7 @@
         <v>1</v>
       </c>
       <c r="M66" s="26">
-        <f t="shared" si="2"/>
+        <f>SUM(G66:L66)</f>
         <v>1</v>
       </c>
       <c r="N66" s="26">
@@ -9085,22 +9128,22 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="40">
-        <v>12028</v>
+        <v>12108</v>
       </c>
       <c r="B67" s="40" t="s">
-        <v>152</v>
+        <v>217</v>
       </c>
       <c r="C67" s="40">
-        <v>1025</v>
+        <v>4803</v>
       </c>
       <c r="D67" s="40" t="s">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="E67" s="40" t="s">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="F67" s="40" t="s">
-        <v>109</v>
+        <v>226</v>
       </c>
       <c r="G67" s="40">
         <v>1</v>
@@ -9115,7 +9158,7 @@
       </c>
       <c r="L67" s="40"/>
       <c r="M67" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G67:L67)</f>
         <v>3</v>
       </c>
       <c r="N67" s="40">
@@ -9130,33 +9173,35 @@
         <v>152</v>
       </c>
       <c r="C68" s="40">
-        <v>1482</v>
+        <v>1025</v>
       </c>
       <c r="D68" s="40" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E68" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F68" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="G68" s="40"/>
-      <c r="H68" s="40">
-        <v>1</v>
-      </c>
-      <c r="I68" s="40"/>
-      <c r="J68" s="40">
-        <v>1</v>
-      </c>
-      <c r="K68" s="40"/>
+      <c r="G68" s="40">
+        <v>1</v>
+      </c>
+      <c r="H68" s="40"/>
+      <c r="I68" s="40">
+        <v>1</v>
+      </c>
+      <c r="J68" s="40"/>
+      <c r="K68" s="40">
+        <v>1</v>
+      </c>
       <c r="L68" s="40"/>
       <c r="M68" s="40">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f>SUM(G68:L68)</f>
+        <v>3</v>
       </c>
       <c r="N68" s="40">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
@@ -9189,7 +9234,7 @@
       <c r="K69" s="40"/>
       <c r="L69" s="40"/>
       <c r="M69" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G69:L69)</f>
         <v>2</v>
       </c>
       <c r="N69" s="40">
@@ -9226,7 +9271,7 @@
       <c r="K70" s="40"/>
       <c r="L70" s="40"/>
       <c r="M70" s="40">
-        <f t="shared" si="2"/>
+        <f>SUM(G70:L70)</f>
         <v>2</v>
       </c>
       <c r="N70" s="40">
@@ -9235,41 +9280,39 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="40">
-        <v>12028</v>
+        <v>11679</v>
       </c>
       <c r="B71" s="40" t="s">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="C71" s="40">
-        <v>1049</v>
+        <v>1011</v>
       </c>
       <c r="D71" s="40" t="s">
-        <v>322</v>
+        <v>282</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="F71" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="G71" s="40">
-        <v>1</v>
-      </c>
-      <c r="H71" s="40"/>
-      <c r="I71" s="40">
-        <v>1</v>
-      </c>
-      <c r="J71" s="40"/>
-      <c r="K71" s="40">
-        <v>1</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="G71" s="40"/>
+      <c r="H71" s="40">
+        <v>1</v>
+      </c>
+      <c r="I71" s="40"/>
+      <c r="J71" s="40">
+        <v>1</v>
+      </c>
+      <c r="K71" s="40"/>
       <c r="L71" s="40"/>
       <c r="M71" s="40">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f>SUM(G71:L71)</f>
+        <v>2</v>
       </c>
       <c r="N71" s="40">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
@@ -9300,7 +9343,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="26">
-        <f t="shared" ref="M72:M103" si="3">SUM(G72:L72)</f>
+        <f>SUM(G72:L72)</f>
         <v>1</v>
       </c>
       <c r="N72" s="26">
@@ -9309,59 +9352,61 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="40">
-        <v>12028</v>
+        <v>10931</v>
       </c>
       <c r="B73" s="40" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="C73" s="40">
-        <v>9346</v>
+        <v>9345</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>324</v>
+        <v>257</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>164</v>
+        <v>9</v>
       </c>
       <c r="F73" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="G73" s="40"/>
-      <c r="H73" s="40">
-        <v>1</v>
-      </c>
-      <c r="I73" s="40"/>
-      <c r="J73" s="40">
-        <v>1</v>
-      </c>
-      <c r="K73" s="40"/>
+        <v>8</v>
+      </c>
+      <c r="G73" s="40">
+        <v>1</v>
+      </c>
+      <c r="H73" s="40"/>
+      <c r="I73" s="40">
+        <v>1</v>
+      </c>
+      <c r="J73" s="40"/>
+      <c r="K73" s="40">
+        <v>1</v>
+      </c>
       <c r="L73" s="40"/>
       <c r="M73" s="40">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f>SUM(G73:L73)</f>
+        <v>3</v>
       </c>
       <c r="N73" s="40">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="40">
-        <v>12028</v>
+        <v>12155</v>
       </c>
       <c r="B74" s="40" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="C74" s="40">
-        <v>11879</v>
+        <v>548</v>
       </c>
       <c r="D74" s="40" t="s">
-        <v>325</v>
+        <v>382</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="F74" s="40" t="s">
-        <v>109</v>
+        <v>246</v>
       </c>
       <c r="G74" s="40">
         <v>1</v>
@@ -9376,11 +9421,11 @@
       </c>
       <c r="L74" s="40"/>
       <c r="M74" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G74:L74)</f>
         <v>3</v>
       </c>
       <c r="N74" s="40">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
@@ -9415,7 +9460,7 @@
       </c>
       <c r="L75" s="40"/>
       <c r="M75" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G75:L75)</f>
         <v>3</v>
       </c>
       <c r="N75" s="40">
@@ -9452,7 +9497,7 @@
       <c r="K76" s="26"/>
       <c r="L76" s="26"/>
       <c r="M76" s="26">
-        <f t="shared" si="3"/>
+        <f>SUM(G76:L76)</f>
         <v>2</v>
       </c>
       <c r="N76" s="26">
@@ -9461,41 +9506,39 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="40">
-        <v>12027</v>
+        <v>12087</v>
       </c>
       <c r="B77" s="40" t="s">
-        <v>404</v>
+        <v>233</v>
       </c>
       <c r="C77" s="40">
-        <v>9347</v>
+        <v>10947</v>
       </c>
       <c r="D77" s="40" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="E77" s="40" t="s">
-        <v>172</v>
+        <v>243</v>
       </c>
       <c r="F77" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="G77" s="40">
-        <v>1</v>
-      </c>
-      <c r="H77" s="40"/>
-      <c r="I77" s="40">
-        <v>1</v>
-      </c>
-      <c r="J77" s="40"/>
-      <c r="K77" s="40">
-        <v>1</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="G77" s="40"/>
+      <c r="H77" s="40">
+        <v>1</v>
+      </c>
+      <c r="I77" s="40"/>
+      <c r="J77" s="40">
+        <v>1</v>
+      </c>
+      <c r="K77" s="40"/>
       <c r="L77" s="40"/>
       <c r="M77" s="40">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f>SUM(G77:L77)</f>
+        <v>2</v>
       </c>
       <c r="N77" s="40">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -9532,7 +9575,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G78:L78)</f>
         <v>4</v>
       </c>
       <c r="N78" s="40">
@@ -9571,7 +9614,7 @@
       </c>
       <c r="L79" s="40"/>
       <c r="M79" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G79:L79)</f>
         <v>3</v>
       </c>
       <c r="N79" s="40">
@@ -9608,7 +9651,7 @@
       <c r="K80" s="40"/>
       <c r="L80" s="40"/>
       <c r="M80" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G80:L80)</f>
         <v>2</v>
       </c>
       <c r="N80" s="40">
@@ -9645,7 +9688,7 @@
       <c r="K81" s="40"/>
       <c r="L81" s="40"/>
       <c r="M81" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G81:L81)</f>
         <v>2</v>
       </c>
       <c r="N81" s="40">
@@ -9686,7 +9729,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G82:L82)</f>
         <v>4</v>
       </c>
       <c r="N82" s="40">
@@ -9723,7 +9766,7 @@
       <c r="K83" s="40"/>
       <c r="L83" s="40"/>
       <c r="M83" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G83:L83)</f>
         <v>2</v>
       </c>
       <c r="N83" s="40">
@@ -9760,7 +9803,7 @@
       </c>
       <c r="L84" s="26"/>
       <c r="M84" s="26">
-        <f t="shared" si="3"/>
+        <f>SUM(G84:L84)</f>
         <v>2</v>
       </c>
       <c r="N84" s="26">
@@ -9806,7 +9849,7 @@
       <c r="K85" s="26"/>
       <c r="L85" s="26"/>
       <c r="M85" s="26">
-        <f t="shared" si="3"/>
+        <f>SUM(G85:L85)</f>
         <v>2</v>
       </c>
       <c r="N85" s="26">
@@ -9854,7 +9897,7 @@
       </c>
       <c r="L86" s="40"/>
       <c r="M86" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G86:L86)</f>
         <v>3</v>
       </c>
       <c r="N86" s="40">
@@ -9893,7 +9936,7 @@
       </c>
       <c r="L87" s="40"/>
       <c r="M87" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G87:L87)</f>
         <v>3</v>
       </c>
       <c r="N87" s="40">
@@ -9928,7 +9971,7 @@
       <c r="K88" s="26"/>
       <c r="L88" s="26"/>
       <c r="M88" s="26">
-        <f t="shared" si="3"/>
+        <f>SUM(G88:L88)</f>
         <v>1</v>
       </c>
       <c r="N88" s="26">
@@ -9967,7 +10010,7 @@
       </c>
       <c r="L89" s="40"/>
       <c r="M89" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G89:L89)</f>
         <v>3</v>
       </c>
       <c r="N89" s="40">
@@ -10002,7 +10045,7 @@
       <c r="K90" s="26"/>
       <c r="L90" s="26"/>
       <c r="M90" s="26">
-        <f t="shared" si="3"/>
+        <f>SUM(G90:L90)</f>
         <v>1</v>
       </c>
       <c r="N90" s="26">
@@ -10039,7 +10082,7 @@
       <c r="K91" s="26"/>
       <c r="L91" s="26"/>
       <c r="M91" s="26">
-        <f t="shared" si="3"/>
+        <f>SUM(G91:L91)</f>
         <v>2</v>
       </c>
       <c r="N91" s="26">
@@ -10083,7 +10126,7 @@
       <c r="K92" s="26"/>
       <c r="L92" s="26"/>
       <c r="M92" s="26">
-        <f t="shared" si="3"/>
+        <f>SUM(G92:L92)</f>
         <v>1</v>
       </c>
       <c r="N92" s="26">
@@ -10092,41 +10135,41 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="40">
-        <v>12079</v>
+        <v>11679</v>
       </c>
       <c r="B93" s="40" t="s">
-        <v>403</v>
+        <v>87</v>
       </c>
       <c r="C93" s="40">
-        <v>4522</v>
+        <v>10948</v>
       </c>
       <c r="D93" s="40" t="s">
-        <v>344</v>
+        <v>279</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>200</v>
+        <v>88</v>
       </c>
       <c r="F93" s="40" t="s">
-        <v>201</v>
-      </c>
-      <c r="G93" s="40"/>
-      <c r="H93" s="40">
-        <v>1</v>
-      </c>
-      <c r="I93" s="40"/>
-      <c r="J93" s="40">
-        <v>1</v>
-      </c>
-      <c r="K93" s="40"/>
-      <c r="L93" s="40">
-        <v>1</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G93" s="40">
+        <v>1</v>
+      </c>
+      <c r="H93" s="40"/>
+      <c r="I93" s="40">
+        <v>1</v>
+      </c>
+      <c r="J93" s="40"/>
+      <c r="K93" s="40">
+        <v>1</v>
+      </c>
+      <c r="L93" s="40"/>
       <c r="M93" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G93:L93)</f>
         <v>3</v>
       </c>
       <c r="N93" s="40">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
@@ -10161,7 +10204,7 @@
         <v>1</v>
       </c>
       <c r="M94" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G94:L94)</f>
         <v>3</v>
       </c>
       <c r="N94" s="40">
@@ -10198,7 +10241,7 @@
       <c r="K95" s="40"/>
       <c r="L95" s="40"/>
       <c r="M95" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G95:L95)</f>
         <v>2</v>
       </c>
       <c r="N95" s="40">
@@ -10207,39 +10250,41 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="40">
-        <v>12076</v>
+        <v>12028</v>
       </c>
       <c r="B96" s="40" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="C96" s="40">
-        <v>838</v>
+        <v>1049</v>
       </c>
       <c r="D96" s="40" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="E96" s="40" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="F96" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="G96" s="40"/>
-      <c r="H96" s="40">
-        <v>1</v>
-      </c>
-      <c r="I96" s="40"/>
-      <c r="J96" s="40">
-        <v>1</v>
-      </c>
-      <c r="K96" s="40"/>
+        <v>161</v>
+      </c>
+      <c r="G96" s="40">
+        <v>1</v>
+      </c>
+      <c r="H96" s="40"/>
+      <c r="I96" s="40">
+        <v>1</v>
+      </c>
+      <c r="J96" s="40"/>
+      <c r="K96" s="40">
+        <v>1</v>
+      </c>
       <c r="L96" s="40"/>
       <c r="M96" s="40">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f>SUM(G96:L96)</f>
+        <v>3</v>
       </c>
       <c r="N96" s="40">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
@@ -10270,7 +10315,7 @@
       <c r="K97" s="40"/>
       <c r="L97" s="40"/>
       <c r="M97" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G97:L97)</f>
         <v>1</v>
       </c>
       <c r="N97" s="40">
@@ -10279,41 +10324,39 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="40">
-        <v>12076</v>
+        <v>12082</v>
       </c>
       <c r="B98" s="40" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C98" s="40">
-        <v>9341</v>
+        <v>2351</v>
       </c>
       <c r="D98" s="40" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E98" s="40" t="s">
-        <v>209</v>
+        <v>65</v>
       </c>
       <c r="F98" s="40" t="s">
-        <v>208</v>
-      </c>
-      <c r="G98" s="40">
-        <v>1</v>
-      </c>
-      <c r="H98" s="40"/>
-      <c r="I98" s="40">
-        <v>1</v>
-      </c>
-      <c r="J98" s="40"/>
-      <c r="K98" s="40">
-        <v>1</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G98" s="40"/>
+      <c r="H98" s="40">
+        <v>1</v>
+      </c>
+      <c r="I98" s="40"/>
+      <c r="J98" s="40">
+        <v>1</v>
+      </c>
+      <c r="K98" s="40"/>
       <c r="L98" s="40"/>
       <c r="M98" s="40">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f>SUM(G98:L98)</f>
+        <v>2</v>
       </c>
       <c r="N98" s="40">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
@@ -10346,7 +10389,7 @@
       </c>
       <c r="L99" s="26"/>
       <c r="M99" s="26">
-        <f t="shared" si="3"/>
+        <f>SUM(G99:L99)</f>
         <v>2</v>
       </c>
       <c r="N99" s="26">
@@ -10383,7 +10426,7 @@
       <c r="K100" s="26"/>
       <c r="L100" s="26"/>
       <c r="M100" s="26">
-        <f t="shared" si="3"/>
+        <f>SUM(G100:L100)</f>
         <v>2</v>
       </c>
       <c r="N100" s="26">
@@ -10392,22 +10435,22 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="40">
-        <v>12076</v>
+        <v>11868</v>
       </c>
       <c r="B101" s="40" t="s">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="C101" s="40">
-        <v>2309</v>
+        <v>9602</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>352</v>
+        <v>302</v>
       </c>
       <c r="E101" s="40" t="s">
-        <v>212</v>
+        <v>129</v>
       </c>
       <c r="F101" s="40" t="s">
-        <v>208</v>
+        <v>112</v>
       </c>
       <c r="G101" s="40"/>
       <c r="H101" s="40">
@@ -10420,7 +10463,7 @@
       <c r="K101" s="40"/>
       <c r="L101" s="40"/>
       <c r="M101" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G101:L101)</f>
         <v>2</v>
       </c>
       <c r="N101" s="40">
@@ -10461,7 +10504,7 @@
         <v>1</v>
       </c>
       <c r="M102" s="40">
-        <f t="shared" si="3"/>
+        <f>SUM(G102:L102)</f>
         <v>4</v>
       </c>
       <c r="N102" s="40">
@@ -10470,22 +10513,22 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="40">
-        <v>12076</v>
+        <v>12028</v>
       </c>
       <c r="B103" s="40" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="C103" s="40">
-        <v>942</v>
+        <v>11879</v>
       </c>
       <c r="D103" s="40" t="s">
-        <v>354</v>
+        <v>325</v>
       </c>
       <c r="E103" s="40" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="F103" s="40" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="G103" s="40">
         <v>1</v>
@@ -10498,35 +10541,33 @@
       <c r="K103" s="40">
         <v>1</v>
       </c>
-      <c r="L103" s="40">
-        <v>1</v>
-      </c>
+      <c r="L103" s="40"/>
       <c r="M103" s="40">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f>SUM(G103:L103)</f>
+        <v>3</v>
       </c>
       <c r="N103" s="40">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="40">
-        <v>12076</v>
+        <v>11023</v>
       </c>
       <c r="B104" s="40" t="s">
-        <v>205</v>
+        <v>36</v>
       </c>
       <c r="C104" s="40">
-        <v>11775</v>
+        <v>4393</v>
       </c>
       <c r="D104" s="40" t="s">
-        <v>355</v>
+        <v>271</v>
       </c>
       <c r="E104" s="40" t="s">
-        <v>215</v>
+        <v>42</v>
       </c>
       <c r="F104" s="40" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G104" s="40"/>
       <c r="H104" s="40">
@@ -10539,31 +10580,31 @@
       <c r="K104" s="40"/>
       <c r="L104" s="40"/>
       <c r="M104" s="40">
-        <f t="shared" ref="M104:M134" si="4">SUM(G104:L104)</f>
+        <f>SUM(G104:L104)</f>
         <v>2</v>
       </c>
       <c r="N104" s="40">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="40">
-        <v>12080</v>
+        <v>11932</v>
       </c>
       <c r="B105" s="40" t="s">
-        <v>216</v>
+        <v>130</v>
       </c>
       <c r="C105" s="40">
-        <v>1004</v>
+        <v>958</v>
       </c>
       <c r="D105" s="40" t="s">
-        <v>356</v>
+        <v>304</v>
       </c>
       <c r="E105" s="40" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="F105" s="40" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="G105" s="40">
         <v>1</v>
@@ -10578,11 +10619,11 @@
       </c>
       <c r="L105" s="40"/>
       <c r="M105" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G105:L105)</f>
         <v>3</v>
       </c>
       <c r="N105" s="40">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
@@ -10617,7 +10658,7 @@
       </c>
       <c r="L106" s="40"/>
       <c r="M106" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G106:L106)</f>
         <v>3</v>
       </c>
       <c r="N106" s="40">
@@ -10626,39 +10667,41 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="40">
-        <v>12082</v>
+        <v>12108</v>
       </c>
       <c r="B107" s="40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C107" s="40">
-        <v>2351</v>
+        <v>9631</v>
       </c>
       <c r="D107" s="40" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="E107" s="40" t="s">
-        <v>65</v>
+        <v>232</v>
       </c>
       <c r="F107" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="G107" s="40"/>
-      <c r="H107" s="40">
-        <v>1</v>
-      </c>
-      <c r="I107" s="40"/>
-      <c r="J107" s="40">
-        <v>1</v>
-      </c>
-      <c r="K107" s="40"/>
+        <v>58</v>
+      </c>
+      <c r="G107" s="40">
+        <v>1</v>
+      </c>
+      <c r="H107" s="40"/>
+      <c r="I107" s="40">
+        <v>1</v>
+      </c>
+      <c r="J107" s="40"/>
+      <c r="K107" s="40">
+        <v>1</v>
+      </c>
       <c r="L107" s="40"/>
       <c r="M107" s="40">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f>SUM(G107:L107)</f>
+        <v>3</v>
       </c>
       <c r="N107" s="40">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
@@ -10691,7 +10734,7 @@
       <c r="K108" s="26"/>
       <c r="L108" s="26"/>
       <c r="M108" s="26">
-        <f t="shared" si="4"/>
+        <f>SUM(G108:L108)</f>
         <v>2</v>
       </c>
       <c r="N108" s="26">
@@ -10736,7 +10779,7 @@
         <v>1</v>
       </c>
       <c r="M109" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G109:L109)</f>
         <v>6</v>
       </c>
       <c r="N109" s="40">
@@ -10773,7 +10816,7 @@
       <c r="K110" s="40"/>
       <c r="L110" s="40"/>
       <c r="M110" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G110:L110)</f>
         <v>2</v>
       </c>
       <c r="N110" s="40">
@@ -10808,7 +10851,7 @@
       <c r="K111" s="26"/>
       <c r="L111" s="26"/>
       <c r="M111" s="26">
-        <f t="shared" si="4"/>
+        <f>SUM(G111:L111)</f>
         <v>1</v>
       </c>
       <c r="N111" s="26">
@@ -10847,7 +10890,7 @@
         <v>1</v>
       </c>
       <c r="M112" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G112:L112)</f>
         <v>3</v>
       </c>
       <c r="N112" s="40">
@@ -10886,7 +10929,7 @@
         <v>1</v>
       </c>
       <c r="M113" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G113:L113)</f>
         <v>3</v>
       </c>
       <c r="N113" s="40">
@@ -10895,22 +10938,22 @@
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" s="40">
-        <v>12108</v>
+        <v>11868</v>
       </c>
       <c r="B114" s="40" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="C114" s="40">
-        <v>4803</v>
+        <v>1043</v>
       </c>
       <c r="D114" s="40" t="s">
-        <v>367</v>
+        <v>300</v>
       </c>
       <c r="E114" s="40" t="s">
-        <v>225</v>
+        <v>127</v>
       </c>
       <c r="F114" s="40" t="s">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="G114" s="40">
         <v>1</v>
@@ -10925,7 +10968,7 @@
       </c>
       <c r="L114" s="40"/>
       <c r="M114" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G114:L114)</f>
         <v>3</v>
       </c>
       <c r="N114" s="40">
@@ -10964,7 +11007,7 @@
       </c>
       <c r="L115" s="40"/>
       <c r="M115" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G115:L115)</f>
         <v>3</v>
       </c>
       <c r="N115" s="40">
@@ -11001,7 +11044,7 @@
       <c r="K116" s="26"/>
       <c r="L116" s="26"/>
       <c r="M116" s="26">
-        <f t="shared" si="4"/>
+        <f>SUM(G116:L116)</f>
         <v>2</v>
       </c>
       <c r="N116" s="26">
@@ -11045,7 +11088,7 @@
       </c>
       <c r="L117" s="26"/>
       <c r="M117" s="26">
-        <f t="shared" si="4"/>
+        <f>SUM(G117:L117)</f>
         <v>1</v>
       </c>
       <c r="N117" s="26">
@@ -11089,7 +11132,7 @@
       <c r="K118" s="26"/>
       <c r="L118" s="26"/>
       <c r="M118" s="26">
-        <f t="shared" si="4"/>
+        <f>SUM(G118:L118)</f>
         <v>1</v>
       </c>
       <c r="N118" s="26">
@@ -11098,41 +11141,39 @@
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" s="40">
-        <v>12108</v>
+        <v>10931</v>
       </c>
       <c r="B119" s="40" t="s">
-        <v>217</v>
+        <v>22</v>
       </c>
       <c r="C119" s="40">
-        <v>9631</v>
+        <v>337</v>
       </c>
       <c r="D119" s="40" t="s">
-        <v>372</v>
+        <v>260</v>
       </c>
       <c r="E119" s="40" t="s">
-        <v>232</v>
+        <v>14</v>
       </c>
       <c r="F119" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="G119" s="40">
-        <v>1</v>
-      </c>
-      <c r="H119" s="40"/>
-      <c r="I119" s="40">
-        <v>1</v>
-      </c>
-      <c r="J119" s="40"/>
-      <c r="K119" s="40">
-        <v>1</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G119" s="40"/>
+      <c r="H119" s="40">
+        <v>1</v>
+      </c>
+      <c r="I119" s="40"/>
+      <c r="J119" s="40">
+        <v>1</v>
+      </c>
+      <c r="K119" s="40"/>
       <c r="L119" s="40"/>
       <c r="M119" s="40">
-        <f t="shared" si="4"/>
-        <v>3</v>
+        <f>SUM(G119:L119)</f>
+        <v>2</v>
       </c>
       <c r="N119" s="40">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.25">
@@ -11169,7 +11210,7 @@
         <v>1</v>
       </c>
       <c r="M120" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G120:L120)</f>
         <v>4</v>
       </c>
       <c r="N120" s="40">
@@ -11178,22 +11219,22 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="40">
-        <v>12087</v>
+        <v>11023</v>
       </c>
       <c r="B121" s="40" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="C121" s="40">
-        <v>1006</v>
+        <v>4029</v>
       </c>
       <c r="D121" s="40" t="s">
-        <v>373</v>
+        <v>275</v>
       </c>
       <c r="E121" s="40" t="s">
-        <v>235</v>
+        <v>47</v>
       </c>
       <c r="F121" s="40" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="G121" s="40">
         <v>1</v>
@@ -11208,11 +11249,11 @@
       </c>
       <c r="L121" s="40"/>
       <c r="M121" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G121:L121)</f>
         <v>3</v>
       </c>
       <c r="N121" s="40">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
@@ -11243,7 +11284,7 @@
       </c>
       <c r="L122" s="26"/>
       <c r="M122" s="26">
-        <f t="shared" si="4"/>
+        <f>SUM(G122:L122)</f>
         <v>1</v>
       </c>
       <c r="N122" s="26">
@@ -11278,7 +11319,7 @@
       <c r="K123" s="26"/>
       <c r="L123" s="26"/>
       <c r="M123" s="26">
-        <f t="shared" si="4"/>
+        <f>SUM(G123:L123)</f>
         <v>1</v>
       </c>
       <c r="N123" s="26">
@@ -11315,7 +11356,7 @@
         <v>1</v>
       </c>
       <c r="M124" s="26">
-        <f t="shared" si="4"/>
+        <f>SUM(G124:L124)</f>
         <v>2</v>
       </c>
       <c r="N124" s="26">
@@ -11333,22 +11374,22 @@
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" s="40">
-        <v>12087</v>
+        <v>12076</v>
       </c>
       <c r="B125" s="40" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="C125" s="40">
-        <v>954</v>
+        <v>2309</v>
       </c>
       <c r="D125" s="40" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="E125" s="40" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="F125" s="40" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="G125" s="40"/>
       <c r="H125" s="40">
@@ -11361,11 +11402,11 @@
       <c r="K125" s="40"/>
       <c r="L125" s="40"/>
       <c r="M125" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G125:L125)</f>
         <v>2</v>
       </c>
       <c r="N125" s="40">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
@@ -11400,7 +11441,7 @@
       </c>
       <c r="L126" s="40"/>
       <c r="M126" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G126:L126)</f>
         <v>3</v>
       </c>
       <c r="N126" s="40">
@@ -11437,7 +11478,7 @@
       <c r="K127" s="40"/>
       <c r="L127" s="40"/>
       <c r="M127" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G127:L127)</f>
         <v>2</v>
       </c>
       <c r="N127" s="40">
@@ -11474,7 +11515,7 @@
       <c r="K128" s="40"/>
       <c r="L128" s="40"/>
       <c r="M128" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G128:L128)</f>
         <v>2</v>
       </c>
       <c r="N128" s="40">
@@ -11483,22 +11524,22 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="40">
-        <v>12087</v>
+        <v>11678</v>
       </c>
       <c r="B129" s="40" t="s">
-        <v>233</v>
+        <v>95</v>
       </c>
       <c r="C129" s="40">
-        <v>10947</v>
+        <v>950</v>
       </c>
       <c r="D129" s="40" t="s">
-        <v>381</v>
+        <v>291</v>
       </c>
       <c r="E129" s="40" t="s">
-        <v>243</v>
+        <v>106</v>
       </c>
       <c r="F129" s="40" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G129" s="40"/>
       <c r="H129" s="40">
@@ -11508,49 +11549,51 @@
       <c r="J129" s="40">
         <v>1</v>
       </c>
-      <c r="K129" s="40"/>
+      <c r="K129" s="40">
+        <v>1</v>
+      </c>
       <c r="L129" s="40"/>
       <c r="M129" s="40">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f>SUM(G129:L129)</f>
+        <v>3</v>
       </c>
       <c r="N129" s="40">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" s="40">
-        <v>12155</v>
+        <v>11023</v>
       </c>
       <c r="B130" s="40" t="s">
-        <v>244</v>
+        <v>36</v>
       </c>
       <c r="C130" s="40">
-        <v>548</v>
+        <v>1058</v>
       </c>
       <c r="D130" s="40" t="s">
-        <v>382</v>
+        <v>278</v>
       </c>
       <c r="E130" s="40" t="s">
-        <v>245</v>
+        <v>52</v>
       </c>
       <c r="F130" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="G130" s="40">
-        <v>1</v>
-      </c>
-      <c r="H130" s="40"/>
-      <c r="I130" s="40">
-        <v>1</v>
-      </c>
-      <c r="J130" s="40"/>
-      <c r="K130" s="40">
-        <v>1</v>
-      </c>
-      <c r="L130" s="40"/>
+        <v>53</v>
+      </c>
+      <c r="G130" s="40"/>
+      <c r="H130" s="40">
+        <v>1</v>
+      </c>
+      <c r="I130" s="40"/>
+      <c r="J130" s="40">
+        <v>1</v>
+      </c>
+      <c r="K130" s="40"/>
+      <c r="L130" s="40">
+        <v>1</v>
+      </c>
       <c r="M130" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G130:L130)</f>
         <v>3</v>
       </c>
       <c r="N130" s="40">
@@ -11587,7 +11630,7 @@
       <c r="K131" s="40"/>
       <c r="L131" s="40"/>
       <c r="M131" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G131:L131)</f>
         <v>2</v>
       </c>
       <c r="N131" s="40">
@@ -11596,22 +11639,22 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" s="40">
-        <v>12155</v>
+        <v>12080</v>
       </c>
       <c r="B132" s="40" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="C132" s="40">
-        <v>976</v>
+        <v>1004</v>
       </c>
       <c r="D132" s="40" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="E132" s="40" t="s">
-        <v>249</v>
+        <v>61</v>
       </c>
       <c r="F132" s="40" t="s">
-        <v>248</v>
+        <v>62</v>
       </c>
       <c r="G132" s="40">
         <v>1</v>
@@ -11626,11 +11669,11 @@
       </c>
       <c r="L132" s="40"/>
       <c r="M132" s="40">
-        <f t="shared" si="4"/>
+        <f>SUM(G132:L132)</f>
         <v>3</v>
       </c>
       <c r="N132" s="40">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
@@ -11663,7 +11706,7 @@
       <c r="K133" s="40"/>
       <c r="L133" s="40"/>
       <c r="M133" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="M104:M134" si="2">SUM(G133:L133)</f>
         <v>2</v>
       </c>
       <c r="N133" s="40">
@@ -11708,7 +11751,7 @@
         <v>1</v>
       </c>
       <c r="M134" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="N134" s="40">
@@ -11736,14 +11779,14 @@
   </cols>
   <sheetData>
     <row r="4" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="51" t="s">
         <v>396</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
     </row>
     <row r="5" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D5" s="39" t="s">
@@ -15556,31 +15599,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E1" s="59">
+      <c r="E1" s="45">
         <f>SUM(E3:E11)</f>
         <v>4</v>
       </c>
-      <c r="F1" s="59">
+      <c r="F1" s="45">
         <f>SUM(F3:F11)</f>
         <v>4</v>
       </c>
-      <c r="G1" s="59">
+      <c r="G1" s="45">
         <f t="shared" ref="G1:J1" si="0">SUM(G3:G11)</f>
         <v>4</v>
       </c>
-      <c r="H1" s="59">
+      <c r="H1" s="45">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I1" s="59">
+      <c r="I1" s="45">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="J1" s="59">
+      <c r="J1" s="45">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K1" s="59"/>
+      <c r="K1" s="45"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
@@ -15595,25 +15638,25 @@
       <c r="D2" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L2" s="16" t="s">
@@ -15633,19 +15676,19 @@
       <c r="D3" s="40" t="s">
         <v>254</v>
       </c>
-      <c r="E3" s="61">
-        <v>1</v>
-      </c>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61">
-        <v>1</v>
-      </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61">
-        <v>1</v>
-      </c>
-      <c r="J3" s="61"/>
-      <c r="K3" s="61">
+      <c r="E3" s="47">
+        <v>1</v>
+      </c>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47">
+        <v>1</v>
+      </c>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47">
+        <v>1</v>
+      </c>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47">
         <f>SUM(E3:J3)</f>
         <v>3</v>
       </c>
@@ -15666,19 +15709,19 @@
       <c r="D4" s="40" t="s">
         <v>255</v>
       </c>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61">
-        <v>1</v>
-      </c>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61">
-        <v>1</v>
-      </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61">
-        <v>1</v>
-      </c>
-      <c r="K4" s="61">
+      <c r="E4" s="47"/>
+      <c r="F4" s="47">
+        <v>1</v>
+      </c>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47">
+        <v>1</v>
+      </c>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47">
+        <v>1</v>
+      </c>
+      <c r="K4" s="47">
         <f t="shared" ref="K4:K11" si="1">SUM(E4:J4)</f>
         <v>3</v>
       </c>
@@ -15699,17 +15742,17 @@
       <c r="D5" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="62">
+      <c r="E5" s="48">
         <v>0</v>
       </c>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63">
-        <v>1</v>
-      </c>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63">
+      <c r="F5" s="49"/>
+      <c r="G5" s="49">
+        <v>1</v>
+      </c>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -15730,19 +15773,19 @@
       <c r="D6" s="40" t="s">
         <v>257</v>
       </c>
-      <c r="E6" s="61">
-        <v>1</v>
-      </c>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61">
-        <v>1</v>
-      </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61">
-        <v>1</v>
-      </c>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61">
+      <c r="E6" s="47">
+        <v>1</v>
+      </c>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47">
+        <v>1</v>
+      </c>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47">
+        <v>1</v>
+      </c>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -15763,19 +15806,19 @@
       <c r="D7" s="40" t="s">
         <v>258</v>
       </c>
-      <c r="E7" s="61">
-        <v>1</v>
-      </c>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61">
-        <v>1</v>
-      </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61">
-        <v>1</v>
-      </c>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61">
+      <c r="E7" s="47">
+        <v>1</v>
+      </c>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47">
+        <v>1</v>
+      </c>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47">
+        <v>1</v>
+      </c>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -15796,17 +15839,17 @@
       <c r="D8" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="E8" s="63">
-        <v>1</v>
-      </c>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="62">
+      <c r="E8" s="49">
+        <v>1</v>
+      </c>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="48">
         <v>0</v>
       </c>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63">
+      <c r="J8" s="49"/>
+      <c r="K8" s="49">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -15827,17 +15870,17 @@
       <c r="D9" s="40" t="s">
         <v>260</v>
       </c>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61">
-        <v>1</v>
-      </c>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61">
-        <v>1</v>
-      </c>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61">
+      <c r="E9" s="47"/>
+      <c r="F9" s="47">
+        <v>1</v>
+      </c>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47">
+        <v>1</v>
+      </c>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="47">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -15858,19 +15901,19 @@
       <c r="D10" s="40" t="s">
         <v>261</v>
       </c>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61">
-        <v>1</v>
-      </c>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61">
-        <v>1</v>
-      </c>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61">
-        <v>1</v>
-      </c>
-      <c r="K10" s="61">
+      <c r="E10" s="47"/>
+      <c r="F10" s="47">
+        <v>1</v>
+      </c>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47">
+        <v>1</v>
+      </c>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47">
+        <v>1</v>
+      </c>
+      <c r="K10" s="47">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -15891,17 +15934,17 @@
       <c r="D11" s="40" t="s">
         <v>262</v>
       </c>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61">
-        <v>1</v>
-      </c>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61">
-        <v>1</v>
-      </c>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61">
+      <c r="E11" s="47"/>
+      <c r="F11" s="47">
+        <v>1</v>
+      </c>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47">
+        <v>1</v>
+      </c>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -15910,31 +15953,31 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E13" s="59">
+      <c r="E13" s="45">
         <f>SUM(E15:E19)</f>
         <v>3</v>
       </c>
-      <c r="F13" s="59">
+      <c r="F13" s="45">
         <f t="shared" ref="F13:J13" si="2">SUM(F15:F19)</f>
         <v>3</v>
       </c>
-      <c r="G13" s="59">
+      <c r="G13" s="45">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="H13" s="59">
+      <c r="H13" s="45">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I13" s="59">
+      <c r="I13" s="45">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="J13" s="59">
+      <c r="J13" s="45">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K13" s="59"/>
+      <c r="K13" s="45"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
@@ -15949,25 +15992,25 @@
       <c r="D14" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="60" t="s">
+      <c r="E14" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="60" t="s">
+      <c r="F14" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G14" s="60" t="s">
+      <c r="G14" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H14" s="60" t="s">
+      <c r="H14" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I14" s="60" t="s">
+      <c r="I14" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J14" s="60" t="s">
+      <c r="J14" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K14" s="60" t="s">
+      <c r="K14" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L14" s="16" t="s">
@@ -15987,19 +16030,19 @@
       <c r="D15" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="E15" s="63">
-        <v>1</v>
-      </c>
-      <c r="F15" s="63"/>
-      <c r="G15" s="62">
+      <c r="E15" s="49">
+        <v>1</v>
+      </c>
+      <c r="F15" s="49"/>
+      <c r="G15" s="48">
         <v>0</v>
       </c>
-      <c r="H15" s="63"/>
-      <c r="I15" s="62">
+      <c r="H15" s="49"/>
+      <c r="I15" s="48">
         <v>0</v>
       </c>
-      <c r="J15" s="63"/>
-      <c r="K15" s="61">
+      <c r="J15" s="49"/>
+      <c r="K15" s="47">
         <f>SUM(E15:J15)</f>
         <v>1</v>
       </c>
@@ -16020,17 +16063,17 @@
       <c r="D16" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61">
-        <v>1</v>
-      </c>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61">
-        <v>1</v>
-      </c>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61">
+      <c r="E16" s="47"/>
+      <c r="F16" s="47">
+        <v>1</v>
+      </c>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47">
+        <v>1</v>
+      </c>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="47">
         <f t="shared" ref="K16:K19" si="3">SUM(E16:J16)</f>
         <v>2</v>
       </c>
@@ -16051,17 +16094,17 @@
       <c r="D17" s="40" t="s">
         <v>265</v>
       </c>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61">
-        <v>1</v>
-      </c>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61">
-        <v>1</v>
-      </c>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-      <c r="K17" s="61">
+      <c r="E17" s="47"/>
+      <c r="F17" s="47">
+        <v>1</v>
+      </c>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47">
+        <v>1</v>
+      </c>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="47">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
@@ -16082,19 +16125,19 @@
       <c r="D18" s="40" t="s">
         <v>266</v>
       </c>
-      <c r="E18" s="61">
-        <v>1</v>
-      </c>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61">
-        <v>1</v>
-      </c>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61">
-        <v>1</v>
-      </c>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61">
+      <c r="E18" s="47">
+        <v>1</v>
+      </c>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47">
+        <v>1</v>
+      </c>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47">
+        <v>1</v>
+      </c>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -16115,25 +16158,25 @@
       <c r="D19" s="40" t="s">
         <v>267</v>
       </c>
-      <c r="E19" s="61">
-        <v>1</v>
-      </c>
-      <c r="F19" s="61">
-        <v>1</v>
-      </c>
-      <c r="G19" s="61">
-        <v>1</v>
-      </c>
-      <c r="H19" s="61">
-        <v>1</v>
-      </c>
-      <c r="I19" s="61">
-        <v>1</v>
-      </c>
-      <c r="J19" s="61">
-        <v>1</v>
-      </c>
-      <c r="K19" s="61">
+      <c r="E19" s="47">
+        <v>1</v>
+      </c>
+      <c r="F19" s="47">
+        <v>1</v>
+      </c>
+      <c r="G19" s="47">
+        <v>1</v>
+      </c>
+      <c r="H19" s="47">
+        <v>1</v>
+      </c>
+      <c r="I19" s="47">
+        <v>1</v>
+      </c>
+      <c r="J19" s="47">
+        <v>1</v>
+      </c>
+      <c r="K19" s="47">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
@@ -16146,37 +16189,37 @@
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="59">
+      <c r="E21" s="45">
         <f>SUM(E23:E33)</f>
         <v>5</v>
       </c>
-      <c r="F21" s="59">
+      <c r="F21" s="45">
         <f t="shared" ref="F21:J21" si="4">SUM(F23:F33)</f>
         <v>4</v>
       </c>
-      <c r="G21" s="59">
+      <c r="G21" s="45">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="H21" s="59">
+      <c r="H21" s="45">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="I21" s="59">
+      <c r="I21" s="45">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="J21" s="59">
+      <c r="J21" s="45">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="K21" s="59"/>
+      <c r="K21" s="45"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="64" t="s">
+      <c r="B22" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="12" t="s">
@@ -16185,25 +16228,25 @@
       <c r="D22" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="60" t="s">
+      <c r="E22" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F22" s="60" t="s">
+      <c r="F22" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G22" s="60" t="s">
+      <c r="G22" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H22" s="60" t="s">
+      <c r="H22" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I22" s="60" t="s">
+      <c r="I22" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J22" s="60" t="s">
+      <c r="J22" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K22" s="60" t="s">
+      <c r="K22" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L22" s="16" t="s">
@@ -16211,31 +16254,31 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="61">
+      <c r="A23" s="47">
         <v>11023</v>
       </c>
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="61">
+      <c r="C23" s="47">
         <v>8900003</v>
       </c>
-      <c r="D23" s="61" t="s">
+      <c r="D23" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="E23" s="61">
-        <v>1</v>
-      </c>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61">
-        <v>1</v>
-      </c>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61">
-        <v>1</v>
-      </c>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61">
+      <c r="E23" s="47">
+        <v>1</v>
+      </c>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47">
+        <v>1</v>
+      </c>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47">
+        <v>1</v>
+      </c>
+      <c r="J23" s="47"/>
+      <c r="K23" s="47">
         <f>SUM(E23:J23)</f>
         <v>3</v>
       </c>
@@ -16244,31 +16287,31 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="61">
+      <c r="A24" s="47">
         <v>11023</v>
       </c>
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="61">
+      <c r="C24" s="47">
         <v>9340</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="D24" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61">
-        <v>1</v>
-      </c>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61">
-        <v>1</v>
-      </c>
-      <c r="I24" s="61"/>
-      <c r="J24" s="61">
-        <v>1</v>
-      </c>
-      <c r="K24" s="61">
+      <c r="E24" s="47"/>
+      <c r="F24" s="47">
+        <v>1</v>
+      </c>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47">
+        <v>1</v>
+      </c>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47">
+        <v>1</v>
+      </c>
+      <c r="K24" s="47">
         <f t="shared" ref="K24:K33" si="5">SUM(E24:J24)</f>
         <v>3</v>
       </c>
@@ -16277,29 +16320,29 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="61">
+      <c r="A25" s="47">
         <v>11023</v>
       </c>
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="61">
+      <c r="C25" s="47">
         <v>8900018</v>
       </c>
-      <c r="D25" s="61" t="s">
+      <c r="D25" s="47" t="s">
         <v>270</v>
       </c>
-      <c r="E25" s="61">
-        <v>1</v>
-      </c>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61">
-        <v>1</v>
-      </c>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61">
+      <c r="E25" s="47">
+        <v>1</v>
+      </c>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47">
+        <v>1</v>
+      </c>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
@@ -16308,29 +16351,29 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="61">
+      <c r="A26" s="47">
         <v>11023</v>
       </c>
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="61">
+      <c r="C26" s="47">
         <v>4393</v>
       </c>
-      <c r="D26" s="61" t="s">
+      <c r="D26" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61">
-        <v>1</v>
-      </c>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61">
-        <v>1</v>
-      </c>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61">
+      <c r="E26" s="47"/>
+      <c r="F26" s="47">
+        <v>1</v>
+      </c>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47">
+        <v>1</v>
+      </c>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
@@ -16339,29 +16382,29 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="63">
+      <c r="A27" s="49">
         <v>11023</v>
       </c>
-      <c r="B27" s="63" t="s">
+      <c r="B27" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="63">
+      <c r="C27" s="49">
         <v>3944</v>
       </c>
-      <c r="D27" s="63" t="s">
+      <c r="D27" s="49" t="s">
         <v>272</v>
       </c>
-      <c r="E27" s="63">
-        <v>1</v>
-      </c>
-      <c r="F27" s="63"/>
-      <c r="G27" s="62">
+      <c r="E27" s="49">
+        <v>1</v>
+      </c>
+      <c r="F27" s="49"/>
+      <c r="G27" s="48">
         <v>0</v>
       </c>
-      <c r="H27" s="63"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="63">
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="49">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -16370,31 +16413,31 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="61">
+      <c r="A28" s="47">
         <v>11023</v>
       </c>
-      <c r="B28" s="61" t="s">
+      <c r="B28" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="61">
+      <c r="C28" s="47">
         <v>8900010</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="47" t="s">
         <v>273</v>
       </c>
-      <c r="E28" s="61">
-        <v>1</v>
-      </c>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61">
-        <v>1</v>
-      </c>
-      <c r="H28" s="61"/>
-      <c r="I28" s="61">
-        <v>1</v>
-      </c>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61">
+      <c r="E28" s="47">
+        <v>1</v>
+      </c>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47">
+        <v>1</v>
+      </c>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47">
+        <v>1</v>
+      </c>
+      <c r="J28" s="47"/>
+      <c r="K28" s="47">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -16403,27 +16446,27 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="63">
+      <c r="A29" s="49">
         <v>11023</v>
       </c>
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="63">
+      <c r="C29" s="49">
         <v>4009</v>
       </c>
-      <c r="D29" s="63" t="s">
+      <c r="D29" s="49" t="s">
         <v>274</v>
       </c>
-      <c r="E29" s="63"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63">
-        <v>1</v>
-      </c>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="63">
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49">
+        <v>1</v>
+      </c>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="49">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -16432,31 +16475,31 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="61">
+      <c r="A30" s="47">
         <v>11023</v>
       </c>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="61">
+      <c r="C30" s="47">
         <v>4029</v>
       </c>
-      <c r="D30" s="61" t="s">
+      <c r="D30" s="47" t="s">
         <v>275</v>
       </c>
-      <c r="E30" s="61">
-        <v>1</v>
-      </c>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61">
-        <v>1</v>
-      </c>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61">
-        <v>1</v>
-      </c>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61">
+      <c r="E30" s="47">
+        <v>1</v>
+      </c>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47">
+        <v>1</v>
+      </c>
+      <c r="H30" s="47"/>
+      <c r="I30" s="47">
+        <v>1</v>
+      </c>
+      <c r="J30" s="47"/>
+      <c r="K30" s="47">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -16465,27 +16508,27 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="63">
+      <c r="A31" s="49">
         <v>11023</v>
       </c>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="63">
+      <c r="C31" s="49">
         <v>5047</v>
       </c>
-      <c r="D31" s="63" t="s">
+      <c r="D31" s="49" t="s">
         <v>276</v>
       </c>
-      <c r="E31" s="63"/>
-      <c r="F31" s="63">
-        <v>1</v>
-      </c>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="63"/>
-      <c r="K31" s="63">
+      <c r="E31" s="49"/>
+      <c r="F31" s="49">
+        <v>1</v>
+      </c>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -16494,27 +16537,27 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="61">
+      <c r="A32" s="47">
         <v>11023</v>
       </c>
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="61">
+      <c r="C32" s="47">
         <v>6971169</v>
       </c>
-      <c r="D32" s="61" t="s">
+      <c r="D32" s="47" t="s">
         <v>277</v>
       </c>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61">
-        <v>1</v>
-      </c>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61">
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47">
+        <v>1</v>
+      </c>
+      <c r="J32" s="47"/>
+      <c r="K32" s="47">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -16523,31 +16566,31 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="61">
+      <c r="A33" s="47">
         <v>11023</v>
       </c>
-      <c r="B33" s="61" t="s">
+      <c r="B33" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="61">
+      <c r="C33" s="47">
         <v>1058</v>
       </c>
-      <c r="D33" s="61" t="s">
+      <c r="D33" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61">
-        <v>1</v>
-      </c>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61">
-        <v>1</v>
-      </c>
-      <c r="I33" s="61"/>
-      <c r="J33" s="61">
-        <v>1</v>
-      </c>
-      <c r="K33" s="61">
+      <c r="E33" s="47"/>
+      <c r="F33" s="47">
+        <v>1</v>
+      </c>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47">
+        <v>1</v>
+      </c>
+      <c r="I33" s="47"/>
+      <c r="J33" s="47">
+        <v>1</v>
+      </c>
+      <c r="K33" s="47">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -16570,31 +16613,31 @@
       <c r="L34" s="40"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E35" s="59">
+      <c r="E35" s="45">
         <f>SUM(E37:E41)</f>
         <v>3</v>
       </c>
-      <c r="F35" s="59">
+      <c r="F35" s="45">
         <f t="shared" ref="F35:J35" si="6">SUM(F37:F41)</f>
         <v>3</v>
       </c>
-      <c r="G35" s="59">
+      <c r="G35" s="45">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="H35" s="59">
+      <c r="H35" s="45">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="I35" s="59">
+      <c r="I35" s="45">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="J35" s="59">
+      <c r="J35" s="45">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="K35" s="59"/>
+      <c r="K35" s="45"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="42" t="s">
@@ -16609,25 +16652,25 @@
       <c r="D36" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E36" s="60" t="s">
+      <c r="E36" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F36" s="60" t="s">
+      <c r="F36" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G36" s="60" t="s">
+      <c r="G36" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H36" s="60" t="s">
+      <c r="H36" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I36" s="60" t="s">
+      <c r="I36" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J36" s="60" t="s">
+      <c r="J36" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K36" s="60" t="s">
+      <c r="K36" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L36" s="16" t="s">
@@ -16647,19 +16690,19 @@
       <c r="D37" s="40" t="s">
         <v>279</v>
       </c>
-      <c r="E37" s="61">
-        <v>1</v>
-      </c>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61">
-        <v>1</v>
-      </c>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61">
-        <v>1</v>
-      </c>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61">
+      <c r="E37" s="47">
+        <v>1</v>
+      </c>
+      <c r="F37" s="47"/>
+      <c r="G37" s="47">
+        <v>1</v>
+      </c>
+      <c r="H37" s="47"/>
+      <c r="I37" s="47">
+        <v>1</v>
+      </c>
+      <c r="J37" s="47"/>
+      <c r="K37" s="47">
         <f>SUM(E37:J37)</f>
         <v>3</v>
       </c>
@@ -16680,19 +16723,19 @@
       <c r="D38" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="E38" s="63">
-        <v>1</v>
-      </c>
-      <c r="F38" s="63"/>
-      <c r="G38" s="62">
+      <c r="E38" s="49">
+        <v>1</v>
+      </c>
+      <c r="F38" s="49"/>
+      <c r="G38" s="48">
         <v>0</v>
       </c>
-      <c r="H38" s="63"/>
-      <c r="I38" s="62">
+      <c r="H38" s="49"/>
+      <c r="I38" s="48">
         <v>0</v>
       </c>
-      <c r="J38" s="63"/>
-      <c r="K38" s="63">
+      <c r="J38" s="49"/>
+      <c r="K38" s="49">
         <f t="shared" ref="K38:K41" si="7">SUM(E38:J38)</f>
         <v>1</v>
       </c>
@@ -16713,17 +16756,17 @@
       <c r="D39" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61">
-        <v>1</v>
-      </c>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61">
-        <v>1</v>
-      </c>
-      <c r="I39" s="61"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61">
+      <c r="E39" s="47"/>
+      <c r="F39" s="47">
+        <v>1</v>
+      </c>
+      <c r="G39" s="47"/>
+      <c r="H39" s="47">
+        <v>1</v>
+      </c>
+      <c r="I39" s="47"/>
+      <c r="J39" s="47"/>
+      <c r="K39" s="47">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -16744,17 +16787,17 @@
       <c r="D40" s="40" t="s">
         <v>282</v>
       </c>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61">
-        <v>1</v>
-      </c>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61">
-        <v>1</v>
-      </c>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61">
+      <c r="E40" s="47"/>
+      <c r="F40" s="47">
+        <v>1</v>
+      </c>
+      <c r="G40" s="47"/>
+      <c r="H40" s="47">
+        <v>1</v>
+      </c>
+      <c r="I40" s="47"/>
+      <c r="J40" s="47"/>
+      <c r="K40" s="47">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
@@ -16775,25 +16818,25 @@
       <c r="D41" s="40" t="s">
         <v>283</v>
       </c>
-      <c r="E41" s="61">
-        <v>1</v>
-      </c>
-      <c r="F41" s="61">
-        <v>1</v>
-      </c>
-      <c r="G41" s="61">
-        <v>1</v>
-      </c>
-      <c r="H41" s="61">
-        <v>1</v>
-      </c>
-      <c r="I41" s="61">
-        <v>1</v>
-      </c>
-      <c r="J41" s="61">
-        <v>1</v>
-      </c>
-      <c r="K41" s="61">
+      <c r="E41" s="47">
+        <v>1</v>
+      </c>
+      <c r="F41" s="47">
+        <v>1</v>
+      </c>
+      <c r="G41" s="47">
+        <v>1</v>
+      </c>
+      <c r="H41" s="47">
+        <v>1</v>
+      </c>
+      <c r="I41" s="47">
+        <v>1</v>
+      </c>
+      <c r="J41" s="47">
+        <v>1</v>
+      </c>
+      <c r="K41" s="47">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
@@ -16802,31 +16845,31 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E43" s="59">
+      <c r="E43" s="45">
         <f>SUM(E45:E53)</f>
         <v>4</v>
       </c>
-      <c r="F43" s="59">
+      <c r="F43" s="45">
         <f t="shared" ref="F43:J43" si="8">SUM(F45:F53)</f>
         <v>5</v>
       </c>
-      <c r="G43" s="59">
+      <c r="G43" s="45">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="H43" s="59">
+      <c r="H43" s="45">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="I43" s="59">
+      <c r="I43" s="45">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="J43" s="59">
+      <c r="J43" s="45">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="K43" s="59"/>
+      <c r="K43" s="45"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="42" t="s">
@@ -16841,25 +16884,25 @@
       <c r="D44" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E44" s="60" t="s">
+      <c r="E44" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F44" s="60" t="s">
+      <c r="F44" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G44" s="60" t="s">
+      <c r="G44" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H44" s="60" t="s">
+      <c r="H44" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I44" s="60" t="s">
+      <c r="I44" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J44" s="60" t="s">
+      <c r="J44" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L44" s="16" t="s">
@@ -16879,19 +16922,19 @@
       <c r="D45" s="40" t="s">
         <v>284</v>
       </c>
-      <c r="E45" s="61">
-        <v>1</v>
-      </c>
-      <c r="F45" s="61"/>
-      <c r="G45" s="61">
-        <v>1</v>
-      </c>
-      <c r="H45" s="61"/>
-      <c r="I45" s="61">
-        <v>1</v>
-      </c>
-      <c r="J45" s="61"/>
-      <c r="K45" s="61">
+      <c r="E45" s="47">
+        <v>1</v>
+      </c>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47">
+        <v>1</v>
+      </c>
+      <c r="H45" s="47"/>
+      <c r="I45" s="47">
+        <v>1</v>
+      </c>
+      <c r="J45" s="47"/>
+      <c r="K45" s="47">
         <f t="shared" ref="K45:K53" si="9">SUM(E45:J45)</f>
         <v>3</v>
       </c>
@@ -16912,19 +16955,19 @@
       <c r="D46" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="E46" s="61">
-        <v>1</v>
-      </c>
-      <c r="F46" s="61"/>
-      <c r="G46" s="61">
-        <v>1</v>
-      </c>
-      <c r="H46" s="61"/>
-      <c r="I46" s="61">
-        <v>1</v>
-      </c>
-      <c r="J46" s="61"/>
-      <c r="K46" s="61">
+      <c r="E46" s="47">
+        <v>1</v>
+      </c>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47">
+        <v>1</v>
+      </c>
+      <c r="H46" s="47"/>
+      <c r="I46" s="47">
+        <v>1</v>
+      </c>
+      <c r="J46" s="47"/>
+      <c r="K46" s="47">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -16945,19 +16988,19 @@
       <c r="D47" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="E47" s="61"/>
-      <c r="F47" s="61">
-        <v>1</v>
-      </c>
-      <c r="G47" s="61"/>
-      <c r="H47" s="61">
-        <v>1</v>
-      </c>
-      <c r="I47" s="61"/>
-      <c r="J47" s="61">
-        <v>1</v>
-      </c>
-      <c r="K47" s="61">
+      <c r="E47" s="47"/>
+      <c r="F47" s="47">
+        <v>1</v>
+      </c>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47">
+        <v>1</v>
+      </c>
+      <c r="I47" s="47"/>
+      <c r="J47" s="47">
+        <v>1</v>
+      </c>
+      <c r="K47" s="47">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -16978,19 +17021,19 @@
       <c r="D48" s="40" t="s">
         <v>287</v>
       </c>
-      <c r="E48" s="61"/>
-      <c r="F48" s="61">
-        <v>1</v>
-      </c>
-      <c r="G48" s="61"/>
-      <c r="H48" s="61">
-        <v>1</v>
-      </c>
-      <c r="I48" s="61"/>
-      <c r="J48" s="61">
-        <v>1</v>
-      </c>
-      <c r="K48" s="61">
+      <c r="E48" s="47"/>
+      <c r="F48" s="47">
+        <v>1</v>
+      </c>
+      <c r="G48" s="47"/>
+      <c r="H48" s="47">
+        <v>1</v>
+      </c>
+      <c r="I48" s="47"/>
+      <c r="J48" s="47">
+        <v>1</v>
+      </c>
+      <c r="K48" s="47">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -17011,19 +17054,19 @@
       <c r="D49" s="40" t="s">
         <v>288</v>
       </c>
-      <c r="E49" s="61">
-        <v>1</v>
-      </c>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61">
-        <v>1</v>
-      </c>
-      <c r="H49" s="61"/>
-      <c r="I49" s="61">
-        <v>1</v>
-      </c>
-      <c r="J49" s="61"/>
-      <c r="K49" s="61">
+      <c r="E49" s="47">
+        <v>1</v>
+      </c>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47">
+        <v>1</v>
+      </c>
+      <c r="H49" s="47"/>
+      <c r="I49" s="47">
+        <v>1</v>
+      </c>
+      <c r="J49" s="47"/>
+      <c r="K49" s="47">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -17044,17 +17087,17 @@
       <c r="D50" s="40" t="s">
         <v>289</v>
       </c>
-      <c r="E50" s="61"/>
-      <c r="F50" s="61">
-        <v>1</v>
-      </c>
-      <c r="G50" s="61"/>
-      <c r="H50" s="61">
-        <v>1</v>
-      </c>
-      <c r="I50" s="61"/>
-      <c r="J50" s="61"/>
-      <c r="K50" s="61">
+      <c r="E50" s="47"/>
+      <c r="F50" s="47">
+        <v>1</v>
+      </c>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47">
+        <v>1</v>
+      </c>
+      <c r="I50" s="47"/>
+      <c r="J50" s="47"/>
+      <c r="K50" s="47">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
@@ -17075,17 +17118,17 @@
       <c r="D51" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="E51" s="63"/>
-      <c r="F51" s="63">
-        <v>1</v>
-      </c>
-      <c r="G51" s="63"/>
-      <c r="H51" s="62">
+      <c r="E51" s="49"/>
+      <c r="F51" s="49">
+        <v>1</v>
+      </c>
+      <c r="G51" s="49"/>
+      <c r="H51" s="48">
         <v>0</v>
       </c>
-      <c r="I51" s="63"/>
-      <c r="J51" s="63"/>
-      <c r="K51" s="63">
+      <c r="I51" s="49"/>
+      <c r="J51" s="49"/>
+      <c r="K51" s="49">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -17106,19 +17149,19 @@
       <c r="D52" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="E52" s="61"/>
-      <c r="F52" s="61">
-        <v>1</v>
-      </c>
-      <c r="G52" s="61"/>
-      <c r="H52" s="61">
-        <v>1</v>
-      </c>
-      <c r="I52" s="61">
-        <v>1</v>
-      </c>
-      <c r="J52" s="61"/>
-      <c r="K52" s="61">
+      <c r="E52" s="47"/>
+      <c r="F52" s="47">
+        <v>1</v>
+      </c>
+      <c r="G52" s="47"/>
+      <c r="H52" s="47">
+        <v>1</v>
+      </c>
+      <c r="I52" s="47">
+        <v>1</v>
+      </c>
+      <c r="J52" s="47"/>
+      <c r="K52" s="47">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -17139,17 +17182,17 @@
       <c r="D53" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="E53" s="63">
-        <v>1</v>
-      </c>
-      <c r="F53" s="63"/>
-      <c r="G53" s="62">
+      <c r="E53" s="49">
+        <v>1</v>
+      </c>
+      <c r="F53" s="49"/>
+      <c r="G53" s="48">
         <v>0</v>
       </c>
-      <c r="H53" s="63"/>
-      <c r="I53" s="63"/>
-      <c r="J53" s="63"/>
-      <c r="K53" s="63">
+      <c r="H53" s="49"/>
+      <c r="I53" s="49"/>
+      <c r="J53" s="49"/>
+      <c r="K53" s="49">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
@@ -17158,31 +17201,31 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E55" s="59">
+      <c r="E55" s="45">
         <f>SUM(E57:E66)</f>
         <v>4</v>
       </c>
-      <c r="F55" s="59">
+      <c r="F55" s="45">
         <f t="shared" ref="F55:J55" si="10">SUM(F57:F66)</f>
         <v>5</v>
       </c>
-      <c r="G55" s="59">
+      <c r="G55" s="45">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="H55" s="59">
+      <c r="H55" s="45">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="I55" s="59">
+      <c r="I55" s="45">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="J55" s="59">
+      <c r="J55" s="45">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="K55" s="59"/>
+      <c r="K55" s="45"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="42" t="s">
@@ -17197,25 +17240,25 @@
       <c r="D56" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E56" s="60" t="s">
+      <c r="E56" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F56" s="60" t="s">
+      <c r="F56" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G56" s="60" t="s">
+      <c r="G56" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H56" s="60" t="s">
+      <c r="H56" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I56" s="60" t="s">
+      <c r="I56" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J56" s="60" t="s">
+      <c r="J56" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K56" s="60" t="s">
+      <c r="K56" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L56" s="16" t="s">
@@ -17235,19 +17278,19 @@
       <c r="D57" s="40" t="s">
         <v>293</v>
       </c>
-      <c r="E57" s="61"/>
-      <c r="F57" s="61">
-        <v>1</v>
-      </c>
-      <c r="G57" s="61"/>
-      <c r="H57" s="61">
-        <v>1</v>
-      </c>
-      <c r="I57" s="61"/>
-      <c r="J57" s="61">
-        <v>1</v>
-      </c>
-      <c r="K57" s="61">
+      <c r="E57" s="47"/>
+      <c r="F57" s="47">
+        <v>1</v>
+      </c>
+      <c r="G57" s="47"/>
+      <c r="H57" s="47">
+        <v>1</v>
+      </c>
+      <c r="I57" s="47"/>
+      <c r="J57" s="47">
+        <v>1</v>
+      </c>
+      <c r="K57" s="47">
         <f t="shared" ref="K57:K66" si="11">SUM(E57:J57)</f>
         <v>3</v>
       </c>
@@ -17268,17 +17311,17 @@
       <c r="D58" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="E58" s="63"/>
-      <c r="F58" s="63">
-        <v>1</v>
-      </c>
-      <c r="G58" s="63"/>
-      <c r="H58" s="62">
+      <c r="E58" s="49"/>
+      <c r="F58" s="49">
+        <v>1</v>
+      </c>
+      <c r="G58" s="49"/>
+      <c r="H58" s="48">
         <v>0</v>
       </c>
-      <c r="I58" s="63"/>
-      <c r="J58" s="63"/>
-      <c r="K58" s="63">
+      <c r="I58" s="49"/>
+      <c r="J58" s="49"/>
+      <c r="K58" s="49">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -17299,17 +17342,17 @@
       <c r="D59" s="40" t="s">
         <v>295</v>
       </c>
-      <c r="E59" s="61"/>
-      <c r="F59" s="61">
-        <v>1</v>
-      </c>
-      <c r="G59" s="61"/>
-      <c r="H59" s="61">
-        <v>1</v>
-      </c>
-      <c r="I59" s="61"/>
-      <c r="J59" s="61"/>
-      <c r="K59" s="61">
+      <c r="E59" s="47"/>
+      <c r="F59" s="47">
+        <v>1</v>
+      </c>
+      <c r="G59" s="47"/>
+      <c r="H59" s="47">
+        <v>1</v>
+      </c>
+      <c r="I59" s="47"/>
+      <c r="J59" s="47"/>
+      <c r="K59" s="47">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
@@ -17330,19 +17373,19 @@
       <c r="D60" s="40" t="s">
         <v>296</v>
       </c>
-      <c r="E60" s="61">
-        <v>1</v>
-      </c>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61">
-        <v>1</v>
-      </c>
-      <c r="H60" s="61"/>
-      <c r="I60" s="61">
-        <v>1</v>
-      </c>
-      <c r="J60" s="61"/>
-      <c r="K60" s="61">
+      <c r="E60" s="47">
+        <v>1</v>
+      </c>
+      <c r="F60" s="47"/>
+      <c r="G60" s="47">
+        <v>1</v>
+      </c>
+      <c r="H60" s="47"/>
+      <c r="I60" s="47">
+        <v>1</v>
+      </c>
+      <c r="J60" s="47"/>
+      <c r="K60" s="47">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
@@ -17363,19 +17406,19 @@
       <c r="D61" s="40" t="s">
         <v>297</v>
       </c>
-      <c r="E61" s="61">
-        <v>1</v>
-      </c>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61">
-        <v>1</v>
-      </c>
-      <c r="H61" s="61"/>
-      <c r="I61" s="61">
-        <v>1</v>
-      </c>
-      <c r="J61" s="61"/>
-      <c r="K61" s="61">
+      <c r="E61" s="47">
+        <v>1</v>
+      </c>
+      <c r="F61" s="47"/>
+      <c r="G61" s="47">
+        <v>1</v>
+      </c>
+      <c r="H61" s="47"/>
+      <c r="I61" s="47">
+        <v>1</v>
+      </c>
+      <c r="J61" s="47"/>
+      <c r="K61" s="47">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
@@ -17396,19 +17439,19 @@
       <c r="D62" s="40" t="s">
         <v>298</v>
       </c>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61">
-        <v>1</v>
-      </c>
-      <c r="G62" s="61"/>
-      <c r="H62" s="61">
-        <v>1</v>
-      </c>
-      <c r="I62" s="61"/>
-      <c r="J62" s="61">
-        <v>1</v>
-      </c>
-      <c r="K62" s="61">
+      <c r="E62" s="47"/>
+      <c r="F62" s="47">
+        <v>1</v>
+      </c>
+      <c r="G62" s="47"/>
+      <c r="H62" s="47">
+        <v>1</v>
+      </c>
+      <c r="I62" s="47"/>
+      <c r="J62" s="47">
+        <v>1</v>
+      </c>
+      <c r="K62" s="47">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
@@ -17429,19 +17472,19 @@
       <c r="D63" s="40" t="s">
         <v>299</v>
       </c>
-      <c r="E63" s="61">
-        <v>1</v>
-      </c>
-      <c r="F63" s="61"/>
-      <c r="G63" s="61">
-        <v>1</v>
-      </c>
-      <c r="H63" s="61"/>
-      <c r="I63" s="61">
-        <v>1</v>
-      </c>
-      <c r="J63" s="61"/>
-      <c r="K63" s="61">
+      <c r="E63" s="47">
+        <v>1</v>
+      </c>
+      <c r="F63" s="47"/>
+      <c r="G63" s="47">
+        <v>1</v>
+      </c>
+      <c r="H63" s="47"/>
+      <c r="I63" s="47">
+        <v>1</v>
+      </c>
+      <c r="J63" s="47"/>
+      <c r="K63" s="47">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
@@ -17462,19 +17505,19 @@
       <c r="D64" s="40" t="s">
         <v>300</v>
       </c>
-      <c r="E64" s="61">
-        <v>1</v>
-      </c>
-      <c r="F64" s="61"/>
-      <c r="G64" s="61">
-        <v>1</v>
-      </c>
-      <c r="H64" s="61"/>
-      <c r="I64" s="61">
-        <v>1</v>
-      </c>
-      <c r="J64" s="61"/>
-      <c r="K64" s="61">
+      <c r="E64" s="47">
+        <v>1</v>
+      </c>
+      <c r="F64" s="47"/>
+      <c r="G64" s="47">
+        <v>1</v>
+      </c>
+      <c r="H64" s="47"/>
+      <c r="I64" s="47">
+        <v>1</v>
+      </c>
+      <c r="J64" s="47"/>
+      <c r="K64" s="47">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
@@ -17495,17 +17538,17 @@
       <c r="D65" s="26" t="s">
         <v>301</v>
       </c>
-      <c r="E65" s="63"/>
-      <c r="F65" s="63"/>
-      <c r="G65" s="63">
-        <v>1</v>
-      </c>
-      <c r="H65" s="63"/>
-      <c r="I65" s="62">
+      <c r="E65" s="49"/>
+      <c r="F65" s="49"/>
+      <c r="G65" s="49">
+        <v>1</v>
+      </c>
+      <c r="H65" s="49"/>
+      <c r="I65" s="48">
         <v>0</v>
       </c>
-      <c r="J65" s="63"/>
-      <c r="K65" s="63">
+      <c r="J65" s="49"/>
+      <c r="K65" s="49">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
@@ -17526,17 +17569,17 @@
       <c r="D66" s="40" t="s">
         <v>302</v>
       </c>
-      <c r="E66" s="61"/>
-      <c r="F66" s="61">
-        <v>1</v>
-      </c>
-      <c r="G66" s="61"/>
-      <c r="H66" s="61">
-        <v>1</v>
-      </c>
-      <c r="I66" s="61"/>
-      <c r="J66" s="61"/>
-      <c r="K66" s="61">
+      <c r="E66" s="47"/>
+      <c r="F66" s="47">
+        <v>1</v>
+      </c>
+      <c r="G66" s="47"/>
+      <c r="H66" s="47">
+        <v>1</v>
+      </c>
+      <c r="I66" s="47"/>
+      <c r="J66" s="47"/>
+      <c r="K66" s="47">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
@@ -17559,31 +17602,31 @@
       <c r="L67" s="40"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E68" s="59">
+      <c r="E68" s="45">
         <f>SUM(E70:E78)</f>
         <v>4</v>
       </c>
-      <c r="F68" s="59">
+      <c r="F68" s="45">
         <f t="shared" ref="F68:J68" si="12">SUM(F70:F78)</f>
         <v>4</v>
       </c>
-      <c r="G68" s="59">
+      <c r="G68" s="45">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="H68" s="59">
+      <c r="H68" s="45">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="I68" s="59">
+      <c r="I68" s="45">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="J68" s="59">
+      <c r="J68" s="45">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="K68" s="59"/>
+      <c r="K68" s="45"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="42" t="s">
@@ -17598,25 +17641,25 @@
       <c r="D69" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E69" s="60" t="s">
+      <c r="E69" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F69" s="60" t="s">
+      <c r="F69" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G69" s="60" t="s">
+      <c r="G69" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H69" s="60" t="s">
+      <c r="H69" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I69" s="60" t="s">
+      <c r="I69" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J69" s="60" t="s">
+      <c r="J69" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K69" s="60" t="s">
+      <c r="K69" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L69" s="16" t="s">
@@ -17636,17 +17679,17 @@
       <c r="D70" s="26" t="s">
         <v>303</v>
       </c>
-      <c r="E70" s="63"/>
-      <c r="F70" s="63">
-        <v>1</v>
-      </c>
-      <c r="G70" s="63"/>
-      <c r="H70" s="62">
+      <c r="E70" s="49"/>
+      <c r="F70" s="49">
+        <v>1</v>
+      </c>
+      <c r="G70" s="49"/>
+      <c r="H70" s="48">
         <v>0</v>
       </c>
-      <c r="I70" s="63"/>
-      <c r="J70" s="63"/>
-      <c r="K70" s="63">
+      <c r="I70" s="49"/>
+      <c r="J70" s="49"/>
+      <c r="K70" s="49">
         <f t="shared" ref="K70:K78" si="13">SUM(E70:J70)</f>
         <v>1</v>
       </c>
@@ -17667,19 +17710,19 @@
       <c r="D71" s="40" t="s">
         <v>304</v>
       </c>
-      <c r="E71" s="61">
-        <v>1</v>
-      </c>
-      <c r="F71" s="61"/>
-      <c r="G71" s="61">
-        <v>1</v>
-      </c>
-      <c r="H71" s="61"/>
-      <c r="I71" s="61">
-        <v>1</v>
-      </c>
-      <c r="J71" s="61"/>
-      <c r="K71" s="61">
+      <c r="E71" s="47">
+        <v>1</v>
+      </c>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47">
+        <v>1</v>
+      </c>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47">
+        <v>1</v>
+      </c>
+      <c r="J71" s="47"/>
+      <c r="K71" s="47">
         <f t="shared" si="13"/>
         <v>3</v>
       </c>
@@ -17700,17 +17743,17 @@
       <c r="D72" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="E72" s="63">
-        <v>1</v>
-      </c>
-      <c r="F72" s="63"/>
-      <c r="G72" s="62">
+      <c r="E72" s="49">
+        <v>1</v>
+      </c>
+      <c r="F72" s="49"/>
+      <c r="G72" s="48">
         <v>0</v>
       </c>
-      <c r="H72" s="63"/>
-      <c r="I72" s="63"/>
-      <c r="J72" s="63"/>
-      <c r="K72" s="63">
+      <c r="H72" s="49"/>
+      <c r="I72" s="49"/>
+      <c r="J72" s="49"/>
+      <c r="K72" s="49">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
@@ -17731,19 +17774,19 @@
       <c r="D73" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="E73" s="61">
-        <v>1</v>
-      </c>
-      <c r="F73" s="61"/>
-      <c r="G73" s="61">
-        <v>1</v>
-      </c>
-      <c r="H73" s="61"/>
-      <c r="I73" s="61">
-        <v>1</v>
-      </c>
-      <c r="J73" s="61"/>
-      <c r="K73" s="61">
+      <c r="E73" s="47">
+        <v>1</v>
+      </c>
+      <c r="F73" s="47"/>
+      <c r="G73" s="47">
+        <v>1</v>
+      </c>
+      <c r="H73" s="47"/>
+      <c r="I73" s="47">
+        <v>1</v>
+      </c>
+      <c r="J73" s="47"/>
+      <c r="K73" s="47">
         <f t="shared" si="13"/>
         <v>3</v>
       </c>
@@ -17764,19 +17807,19 @@
       <c r="D74" s="40" t="s">
         <v>307</v>
       </c>
-      <c r="E74" s="61">
-        <v>1</v>
-      </c>
-      <c r="F74" s="61"/>
-      <c r="G74" s="61">
-        <v>1</v>
-      </c>
-      <c r="H74" s="61"/>
-      <c r="I74" s="61">
-        <v>1</v>
-      </c>
-      <c r="J74" s="61"/>
-      <c r="K74" s="61">
+      <c r="E74" s="47">
+        <v>1</v>
+      </c>
+      <c r="F74" s="47"/>
+      <c r="G74" s="47">
+        <v>1</v>
+      </c>
+      <c r="H74" s="47"/>
+      <c r="I74" s="47">
+        <v>1</v>
+      </c>
+      <c r="J74" s="47"/>
+      <c r="K74" s="47">
         <f t="shared" si="13"/>
         <v>3</v>
       </c>
@@ -17797,19 +17840,19 @@
       <c r="D75" s="26" t="s">
         <v>308</v>
       </c>
-      <c r="E75" s="63"/>
-      <c r="F75" s="63">
-        <v>1</v>
-      </c>
-      <c r="G75" s="63"/>
-      <c r="H75" s="62">
+      <c r="E75" s="49"/>
+      <c r="F75" s="49">
+        <v>1</v>
+      </c>
+      <c r="G75" s="49"/>
+      <c r="H75" s="48">
         <v>0</v>
       </c>
-      <c r="I75" s="63"/>
-      <c r="J75" s="62">
+      <c r="I75" s="49"/>
+      <c r="J75" s="48">
         <v>0</v>
       </c>
-      <c r="K75" s="61">
+      <c r="K75" s="47">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
@@ -17830,17 +17873,17 @@
       <c r="D76" s="26" t="s">
         <v>309</v>
       </c>
-      <c r="E76" s="63"/>
-      <c r="F76" s="63">
-        <v>1</v>
-      </c>
-      <c r="G76" s="63"/>
-      <c r="H76" s="63">
-        <v>1</v>
-      </c>
-      <c r="I76" s="63"/>
-      <c r="J76" s="63"/>
-      <c r="K76" s="61">
+      <c r="E76" s="49"/>
+      <c r="F76" s="49">
+        <v>1</v>
+      </c>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49">
+        <v>1</v>
+      </c>
+      <c r="I76" s="49"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="47">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
@@ -17861,15 +17904,15 @@
       <c r="D77" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="E77" s="63"/>
-      <c r="F77" s="63"/>
-      <c r="G77" s="63"/>
-      <c r="H77" s="63"/>
-      <c r="I77" s="63"/>
-      <c r="J77" s="63">
-        <v>1</v>
-      </c>
-      <c r="K77" s="63">
+      <c r="E77" s="49"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="49"/>
+      <c r="H77" s="49"/>
+      <c r="I77" s="49"/>
+      <c r="J77" s="49">
+        <v>1</v>
+      </c>
+      <c r="K77" s="49">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
@@ -17890,17 +17933,17 @@
       <c r="D78" s="40" t="s">
         <v>311</v>
       </c>
-      <c r="E78" s="61"/>
-      <c r="F78" s="61">
-        <v>1</v>
-      </c>
-      <c r="G78" s="61"/>
-      <c r="H78" s="61">
-        <v>1</v>
-      </c>
-      <c r="I78" s="61"/>
-      <c r="J78" s="61"/>
-      <c r="K78" s="61">
+      <c r="E78" s="47"/>
+      <c r="F78" s="47">
+        <v>1</v>
+      </c>
+      <c r="G78" s="47"/>
+      <c r="H78" s="47">
+        <v>1</v>
+      </c>
+      <c r="I78" s="47"/>
+      <c r="J78" s="47"/>
+      <c r="K78" s="47">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
@@ -17923,31 +17966,31 @@
       <c r="L79" s="40"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E80" s="59">
+      <c r="E80" s="45">
         <f>SUM(E82:E91)</f>
         <v>4</v>
       </c>
-      <c r="F80" s="59">
+      <c r="F80" s="45">
         <f t="shared" ref="F80:J80" si="14">SUM(F82:F91)</f>
         <v>4</v>
       </c>
-      <c r="G80" s="59">
+      <c r="G80" s="45">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="H80" s="59">
+      <c r="H80" s="45">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="I80" s="59">
+      <c r="I80" s="45">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="J80" s="59">
+      <c r="J80" s="45">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="K80" s="59"/>
+      <c r="K80" s="45"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="42" t="s">
@@ -17962,25 +18005,25 @@
       <c r="D81" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E81" s="60" t="s">
+      <c r="E81" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F81" s="60" t="s">
+      <c r="F81" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G81" s="60" t="s">
+      <c r="G81" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H81" s="60" t="s">
+      <c r="H81" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I81" s="60" t="s">
+      <c r="I81" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J81" s="60" t="s">
+      <c r="J81" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K81" s="60" t="s">
+      <c r="K81" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L81" s="16" t="s">
@@ -18000,21 +18043,21 @@
       <c r="D82" s="40" t="s">
         <v>365</v>
       </c>
-      <c r="E82" s="61">
-        <v>1</v>
-      </c>
-      <c r="F82" s="61"/>
-      <c r="G82" s="61">
-        <v>1</v>
-      </c>
-      <c r="H82" s="61"/>
-      <c r="I82" s="61">
-        <v>1</v>
-      </c>
-      <c r="J82" s="61">
-        <v>1</v>
-      </c>
-      <c r="K82" s="61">
+      <c r="E82" s="47">
+        <v>1</v>
+      </c>
+      <c r="F82" s="47"/>
+      <c r="G82" s="47">
+        <v>1</v>
+      </c>
+      <c r="H82" s="47"/>
+      <c r="I82" s="47">
+        <v>1</v>
+      </c>
+      <c r="J82" s="47">
+        <v>1</v>
+      </c>
+      <c r="K82" s="47">
         <f t="shared" ref="K82:K91" si="15">SUM(E82:J82)</f>
         <v>4</v>
       </c>
@@ -18035,19 +18078,19 @@
       <c r="D83" s="40" t="s">
         <v>373</v>
       </c>
-      <c r="E83" s="61">
-        <v>1</v>
-      </c>
-      <c r="F83" s="61"/>
-      <c r="G83" s="61">
-        <v>1</v>
-      </c>
-      <c r="H83" s="61"/>
-      <c r="I83" s="61">
-        <v>1</v>
-      </c>
-      <c r="J83" s="61"/>
-      <c r="K83" s="61">
+      <c r="E83" s="47">
+        <v>1</v>
+      </c>
+      <c r="F83" s="47"/>
+      <c r="G83" s="47">
+        <v>1</v>
+      </c>
+      <c r="H83" s="47"/>
+      <c r="I83" s="47">
+        <v>1</v>
+      </c>
+      <c r="J83" s="47"/>
+      <c r="K83" s="47">
         <f t="shared" si="15"/>
         <v>3</v>
       </c>
@@ -18068,15 +18111,15 @@
       <c r="D84" s="26" t="s">
         <v>374</v>
       </c>
-      <c r="E84" s="63"/>
-      <c r="F84" s="63"/>
-      <c r="G84" s="63"/>
-      <c r="H84" s="63"/>
-      <c r="I84" s="63">
-        <v>1</v>
-      </c>
-      <c r="J84" s="63"/>
-      <c r="K84" s="63">
+      <c r="E84" s="49"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="49"/>
+      <c r="H84" s="49"/>
+      <c r="I84" s="49">
+        <v>1</v>
+      </c>
+      <c r="J84" s="49"/>
+      <c r="K84" s="49">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
@@ -18097,15 +18140,15 @@
       <c r="D85" s="26" t="s">
         <v>375</v>
       </c>
-      <c r="E85" s="63">
-        <v>1</v>
-      </c>
-      <c r="F85" s="63"/>
-      <c r="G85" s="63"/>
-      <c r="H85" s="63"/>
-      <c r="I85" s="63"/>
-      <c r="J85" s="63"/>
-      <c r="K85" s="63">
+      <c r="E85" s="49">
+        <v>1</v>
+      </c>
+      <c r="F85" s="49"/>
+      <c r="G85" s="49"/>
+      <c r="H85" s="49"/>
+      <c r="I85" s="49"/>
+      <c r="J85" s="49"/>
+      <c r="K85" s="49">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
@@ -18126,17 +18169,17 @@
       <c r="D86" s="26" t="s">
         <v>376</v>
       </c>
-      <c r="E86" s="63"/>
-      <c r="F86" s="63"/>
-      <c r="G86" s="63">
-        <v>1</v>
-      </c>
-      <c r="H86" s="63"/>
-      <c r="I86" s="63"/>
-      <c r="J86" s="62">
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="49">
+        <v>1</v>
+      </c>
+      <c r="H86" s="49"/>
+      <c r="I86" s="49"/>
+      <c r="J86" s="48">
         <v>0</v>
       </c>
-      <c r="K86" s="63">
+      <c r="K86" s="49">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
@@ -18157,17 +18200,17 @@
       <c r="D87" s="40" t="s">
         <v>377</v>
       </c>
-      <c r="E87" s="61"/>
-      <c r="F87" s="61">
-        <v>1</v>
-      </c>
-      <c r="G87" s="61"/>
-      <c r="H87" s="61">
-        <v>1</v>
-      </c>
-      <c r="I87" s="61"/>
-      <c r="J87" s="61"/>
-      <c r="K87" s="61">
+      <c r="E87" s="47"/>
+      <c r="F87" s="47">
+        <v>1</v>
+      </c>
+      <c r="G87" s="47"/>
+      <c r="H87" s="47">
+        <v>1</v>
+      </c>
+      <c r="I87" s="47"/>
+      <c r="J87" s="47"/>
+      <c r="K87" s="47">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
@@ -18188,19 +18231,19 @@
       <c r="D88" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="E88" s="61">
-        <v>1</v>
-      </c>
-      <c r="F88" s="61"/>
-      <c r="G88" s="61">
-        <v>1</v>
-      </c>
-      <c r="H88" s="61"/>
-      <c r="I88" s="61">
-        <v>1</v>
-      </c>
-      <c r="J88" s="61"/>
-      <c r="K88" s="61">
+      <c r="E88" s="47">
+        <v>1</v>
+      </c>
+      <c r="F88" s="47"/>
+      <c r="G88" s="47">
+        <v>1</v>
+      </c>
+      <c r="H88" s="47"/>
+      <c r="I88" s="47">
+        <v>1</v>
+      </c>
+      <c r="J88" s="47"/>
+      <c r="K88" s="47">
         <f t="shared" si="15"/>
         <v>3</v>
       </c>
@@ -18221,17 +18264,17 @@
       <c r="D89" s="40" t="s">
         <v>379</v>
       </c>
-      <c r="E89" s="61"/>
-      <c r="F89" s="61">
-        <v>1</v>
-      </c>
-      <c r="G89" s="61"/>
-      <c r="H89" s="61">
-        <v>1</v>
-      </c>
-      <c r="I89" s="61"/>
-      <c r="J89" s="61"/>
-      <c r="K89" s="61">
+      <c r="E89" s="47"/>
+      <c r="F89" s="47">
+        <v>1</v>
+      </c>
+      <c r="G89" s="47"/>
+      <c r="H89" s="47">
+        <v>1</v>
+      </c>
+      <c r="I89" s="47"/>
+      <c r="J89" s="47"/>
+      <c r="K89" s="47">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
@@ -18252,17 +18295,17 @@
       <c r="D90" s="40" t="s">
         <v>380</v>
       </c>
-      <c r="E90" s="61"/>
-      <c r="F90" s="61">
-        <v>1</v>
-      </c>
-      <c r="G90" s="61"/>
-      <c r="H90" s="61">
-        <v>1</v>
-      </c>
-      <c r="I90" s="61"/>
-      <c r="J90" s="61"/>
-      <c r="K90" s="61">
+      <c r="E90" s="47"/>
+      <c r="F90" s="47">
+        <v>1</v>
+      </c>
+      <c r="G90" s="47"/>
+      <c r="H90" s="47">
+        <v>1</v>
+      </c>
+      <c r="I90" s="47"/>
+      <c r="J90" s="47"/>
+      <c r="K90" s="47">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
@@ -18283,17 +18326,17 @@
       <c r="D91" s="40" t="s">
         <v>381</v>
       </c>
-      <c r="E91" s="61"/>
-      <c r="F91" s="61">
-        <v>1</v>
-      </c>
-      <c r="G91" s="61"/>
-      <c r="H91" s="61">
-        <v>1</v>
-      </c>
-      <c r="I91" s="61"/>
-      <c r="J91" s="61"/>
-      <c r="K91" s="61">
+      <c r="E91" s="47"/>
+      <c r="F91" s="47">
+        <v>1</v>
+      </c>
+      <c r="G91" s="47"/>
+      <c r="H91" s="47">
+        <v>1</v>
+      </c>
+      <c r="I91" s="47"/>
+      <c r="J91" s="47"/>
+      <c r="K91" s="47">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
@@ -18316,31 +18359,31 @@
       <c r="L92" s="40"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E93" s="59">
+      <c r="E93" s="45">
         <f>SUM(E95:E104)</f>
         <v>4</v>
       </c>
-      <c r="F93" s="59">
+      <c r="F93" s="45">
         <f t="shared" ref="F93:J93" si="16">SUM(F95:F104)</f>
         <v>4</v>
       </c>
-      <c r="G93" s="59">
+      <c r="G93" s="45">
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="H93" s="59">
+      <c r="H93" s="45">
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="I93" s="59">
+      <c r="I93" s="45">
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="J93" s="59">
+      <c r="J93" s="45">
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K93" s="59"/>
+      <c r="K93" s="45"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="42" t="s">
@@ -18355,25 +18398,25 @@
       <c r="D94" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E94" s="60" t="s">
+      <c r="E94" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F94" s="60" t="s">
+      <c r="F94" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G94" s="60" t="s">
+      <c r="G94" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H94" s="60" t="s">
+      <c r="H94" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I94" s="60" t="s">
+      <c r="I94" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J94" s="60" t="s">
+      <c r="J94" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K94" s="60" t="s">
+      <c r="K94" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L94" s="16" t="s">
@@ -18393,15 +18436,15 @@
       <c r="D95" s="26" t="s">
         <v>317</v>
       </c>
-      <c r="E95" s="63"/>
-      <c r="F95" s="63"/>
-      <c r="G95" s="63"/>
-      <c r="H95" s="63"/>
-      <c r="I95" s="63"/>
-      <c r="J95" s="63">
-        <v>1</v>
-      </c>
-      <c r="K95" s="63">
+      <c r="E95" s="49"/>
+      <c r="F95" s="49"/>
+      <c r="G95" s="49"/>
+      <c r="H95" s="49"/>
+      <c r="I95" s="49"/>
+      <c r="J95" s="49">
+        <v>1</v>
+      </c>
+      <c r="K95" s="49">
         <v>1</v>
       </c>
       <c r="L95" s="26">
@@ -18421,19 +18464,19 @@
       <c r="D96" s="40" t="s">
         <v>318</v>
       </c>
-      <c r="E96" s="61">
-        <v>1</v>
-      </c>
-      <c r="F96" s="61"/>
-      <c r="G96" s="61">
-        <v>1</v>
-      </c>
-      <c r="H96" s="61"/>
-      <c r="I96" s="61">
-        <v>1</v>
-      </c>
-      <c r="J96" s="61"/>
-      <c r="K96" s="61">
+      <c r="E96" s="47">
+        <v>1</v>
+      </c>
+      <c r="F96" s="47"/>
+      <c r="G96" s="47">
+        <v>1</v>
+      </c>
+      <c r="H96" s="47"/>
+      <c r="I96" s="47">
+        <v>1</v>
+      </c>
+      <c r="J96" s="47"/>
+      <c r="K96" s="47">
         <v>3</v>
       </c>
       <c r="L96" s="40">
@@ -18453,17 +18496,17 @@
       <c r="D97" s="40" t="s">
         <v>319</v>
       </c>
-      <c r="E97" s="61"/>
-      <c r="F97" s="61">
-        <v>1</v>
-      </c>
-      <c r="G97" s="61"/>
-      <c r="H97" s="61">
-        <v>1</v>
-      </c>
-      <c r="I97" s="61"/>
-      <c r="J97" s="61"/>
-      <c r="K97" s="61">
+      <c r="E97" s="47"/>
+      <c r="F97" s="47">
+        <v>1</v>
+      </c>
+      <c r="G97" s="47"/>
+      <c r="H97" s="47">
+        <v>1</v>
+      </c>
+      <c r="I97" s="47"/>
+      <c r="J97" s="47"/>
+      <c r="K97" s="47">
         <v>2</v>
       </c>
       <c r="L97" s="40">
@@ -18483,17 +18526,17 @@
       <c r="D98" s="40" t="s">
         <v>320</v>
       </c>
-      <c r="E98" s="61"/>
-      <c r="F98" s="61">
-        <v>1</v>
-      </c>
-      <c r="G98" s="61"/>
-      <c r="H98" s="61">
-        <v>1</v>
-      </c>
-      <c r="I98" s="61"/>
-      <c r="J98" s="61"/>
-      <c r="K98" s="61">
+      <c r="E98" s="47"/>
+      <c r="F98" s="47">
+        <v>1</v>
+      </c>
+      <c r="G98" s="47"/>
+      <c r="H98" s="47">
+        <v>1</v>
+      </c>
+      <c r="I98" s="47"/>
+      <c r="J98" s="47"/>
+      <c r="K98" s="47">
         <v>2</v>
       </c>
       <c r="L98" s="40">
@@ -18513,17 +18556,17 @@
       <c r="D99" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="E99" s="61"/>
-      <c r="F99" s="61">
-        <v>1</v>
-      </c>
-      <c r="G99" s="61"/>
-      <c r="H99" s="61">
-        <v>1</v>
-      </c>
-      <c r="I99" s="61"/>
-      <c r="J99" s="61"/>
-      <c r="K99" s="61">
+      <c r="E99" s="47"/>
+      <c r="F99" s="47">
+        <v>1</v>
+      </c>
+      <c r="G99" s="47"/>
+      <c r="H99" s="47">
+        <v>1</v>
+      </c>
+      <c r="I99" s="47"/>
+      <c r="J99" s="47"/>
+      <c r="K99" s="47">
         <v>2</v>
       </c>
       <c r="L99" s="40">
@@ -18543,19 +18586,19 @@
       <c r="D100" s="40" t="s">
         <v>322</v>
       </c>
-      <c r="E100" s="61">
-        <v>1</v>
-      </c>
-      <c r="F100" s="61"/>
-      <c r="G100" s="61">
-        <v>1</v>
-      </c>
-      <c r="H100" s="61"/>
-      <c r="I100" s="61">
-        <v>1</v>
-      </c>
-      <c r="J100" s="61"/>
-      <c r="K100" s="61">
+      <c r="E100" s="47">
+        <v>1</v>
+      </c>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47">
+        <v>1</v>
+      </c>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47">
+        <v>1</v>
+      </c>
+      <c r="J100" s="47"/>
+      <c r="K100" s="47">
         <v>3</v>
       </c>
       <c r="L100" s="40">
@@ -18575,15 +18618,15 @@
       <c r="D101" s="26" t="s">
         <v>323</v>
       </c>
-      <c r="E101" s="63"/>
-      <c r="F101" s="63"/>
-      <c r="G101" s="63"/>
-      <c r="H101" s="63"/>
-      <c r="I101" s="63"/>
-      <c r="J101" s="63">
-        <v>1</v>
-      </c>
-      <c r="K101" s="63">
+      <c r="E101" s="49"/>
+      <c r="F101" s="49"/>
+      <c r="G101" s="49"/>
+      <c r="H101" s="49"/>
+      <c r="I101" s="49"/>
+      <c r="J101" s="49">
+        <v>1</v>
+      </c>
+      <c r="K101" s="49">
         <v>1</v>
       </c>
       <c r="L101" s="26">
@@ -18603,17 +18646,17 @@
       <c r="D102" s="40" t="s">
         <v>324</v>
       </c>
-      <c r="E102" s="61"/>
-      <c r="F102" s="61">
-        <v>1</v>
-      </c>
-      <c r="G102" s="61"/>
-      <c r="H102" s="61">
-        <v>1</v>
-      </c>
-      <c r="I102" s="61"/>
-      <c r="J102" s="61"/>
-      <c r="K102" s="61">
+      <c r="E102" s="47"/>
+      <c r="F102" s="47">
+        <v>1</v>
+      </c>
+      <c r="G102" s="47"/>
+      <c r="H102" s="47">
+        <v>1</v>
+      </c>
+      <c r="I102" s="47"/>
+      <c r="J102" s="47"/>
+      <c r="K102" s="47">
         <v>2</v>
       </c>
       <c r="L102" s="40">
@@ -18633,19 +18676,19 @@
       <c r="D103" s="40" t="s">
         <v>325</v>
       </c>
-      <c r="E103" s="61">
-        <v>1</v>
-      </c>
-      <c r="F103" s="61"/>
-      <c r="G103" s="61">
-        <v>1</v>
-      </c>
-      <c r="H103" s="61"/>
-      <c r="I103" s="61">
-        <v>1</v>
-      </c>
-      <c r="J103" s="61"/>
-      <c r="K103" s="61">
+      <c r="E103" s="47">
+        <v>1</v>
+      </c>
+      <c r="F103" s="47"/>
+      <c r="G103" s="47">
+        <v>1</v>
+      </c>
+      <c r="H103" s="47"/>
+      <c r="I103" s="47">
+        <v>1</v>
+      </c>
+      <c r="J103" s="47"/>
+      <c r="K103" s="47">
         <v>3</v>
       </c>
       <c r="L103" s="40">
@@ -18665,19 +18708,19 @@
       <c r="D104" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="E104" s="61">
-        <v>1</v>
-      </c>
-      <c r="F104" s="61"/>
-      <c r="G104" s="61">
-        <v>1</v>
-      </c>
-      <c r="H104" s="61"/>
-      <c r="I104" s="61">
-        <v>1</v>
-      </c>
-      <c r="J104" s="61"/>
-      <c r="K104" s="61">
+      <c r="E104" s="47">
+        <v>1</v>
+      </c>
+      <c r="F104" s="47"/>
+      <c r="G104" s="47">
+        <v>1</v>
+      </c>
+      <c r="H104" s="47"/>
+      <c r="I104" s="47">
+        <v>1</v>
+      </c>
+      <c r="J104" s="47"/>
+      <c r="K104" s="47">
         <v>3</v>
       </c>
       <c r="L104" s="40">
@@ -18699,31 +18742,31 @@
       <c r="L105" s="40"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E106" s="59">
+      <c r="E106" s="45">
         <f>SUM(E108:E115)</f>
         <v>4</v>
       </c>
-      <c r="F106" s="59">
+      <c r="F106" s="45">
         <f t="shared" ref="F106:J106" si="17">SUM(F108:F115)</f>
         <v>4</v>
       </c>
-      <c r="G106" s="59">
+      <c r="G106" s="45">
         <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="H106" s="59">
+      <c r="H106" s="45">
         <f t="shared" si="17"/>
         <v>3</v>
       </c>
-      <c r="I106" s="59">
+      <c r="I106" s="45">
         <f t="shared" si="17"/>
         <v>4</v>
       </c>
-      <c r="J106" s="59">
+      <c r="J106" s="45">
         <f t="shared" si="17"/>
         <v>2</v>
       </c>
-      <c r="K106" s="59"/>
+      <c r="K106" s="45"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="42" t="s">
@@ -18738,25 +18781,25 @@
       <c r="D107" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E107" s="60" t="s">
+      <c r="E107" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F107" s="60" t="s">
+      <c r="F107" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G107" s="60" t="s">
+      <c r="G107" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H107" s="60" t="s">
+      <c r="H107" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I107" s="60" t="s">
+      <c r="I107" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J107" s="60" t="s">
+      <c r="J107" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K107" s="60" t="s">
+      <c r="K107" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L107" s="16" t="s">
@@ -18776,17 +18819,17 @@
       <c r="D108" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="E108" s="63"/>
-      <c r="F108" s="63">
-        <v>1</v>
-      </c>
-      <c r="G108" s="63"/>
-      <c r="H108" s="62">
+      <c r="E108" s="49"/>
+      <c r="F108" s="49">
+        <v>1</v>
+      </c>
+      <c r="G108" s="49"/>
+      <c r="H108" s="48">
         <v>0</v>
       </c>
-      <c r="I108" s="63"/>
-      <c r="J108" s="63"/>
-      <c r="K108" s="63">
+      <c r="I108" s="49"/>
+      <c r="J108" s="49"/>
+      <c r="K108" s="49">
         <f t="shared" ref="K108:K115" si="18">SUM(E108:J108)</f>
         <v>1</v>
       </c>
@@ -18807,19 +18850,19 @@
       <c r="D109" s="40" t="s">
         <v>328</v>
       </c>
-      <c r="E109" s="61">
-        <v>1</v>
-      </c>
-      <c r="F109" s="61"/>
-      <c r="G109" s="61">
-        <v>1</v>
-      </c>
-      <c r="H109" s="61"/>
-      <c r="I109" s="61">
-        <v>1</v>
-      </c>
-      <c r="J109" s="61"/>
-      <c r="K109" s="61">
+      <c r="E109" s="47">
+        <v>1</v>
+      </c>
+      <c r="F109" s="47"/>
+      <c r="G109" s="47">
+        <v>1</v>
+      </c>
+      <c r="H109" s="47"/>
+      <c r="I109" s="47">
+        <v>1</v>
+      </c>
+      <c r="J109" s="47"/>
+      <c r="K109" s="47">
         <f t="shared" si="18"/>
         <v>3</v>
       </c>
@@ -18840,21 +18883,21 @@
       <c r="D110" s="40" t="s">
         <v>329</v>
       </c>
-      <c r="E110" s="61">
-        <v>1</v>
-      </c>
-      <c r="F110" s="61"/>
-      <c r="G110" s="61">
-        <v>1</v>
-      </c>
-      <c r="H110" s="61"/>
-      <c r="I110" s="61">
-        <v>1</v>
-      </c>
-      <c r="J110" s="61">
-        <v>1</v>
-      </c>
-      <c r="K110" s="61">
+      <c r="E110" s="47">
+        <v>1</v>
+      </c>
+      <c r="F110" s="47"/>
+      <c r="G110" s="47">
+        <v>1</v>
+      </c>
+      <c r="H110" s="47"/>
+      <c r="I110" s="47">
+        <v>1</v>
+      </c>
+      <c r="J110" s="47">
+        <v>1</v>
+      </c>
+      <c r="K110" s="47">
         <f t="shared" si="18"/>
         <v>4</v>
       </c>
@@ -18875,19 +18918,19 @@
       <c r="D111" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="E111" s="61">
-        <v>1</v>
-      </c>
-      <c r="F111" s="61"/>
-      <c r="G111" s="61">
-        <v>1</v>
-      </c>
-      <c r="H111" s="61"/>
-      <c r="I111" s="61">
-        <v>1</v>
-      </c>
-      <c r="J111" s="61"/>
-      <c r="K111" s="61">
+      <c r="E111" s="47">
+        <v>1</v>
+      </c>
+      <c r="F111" s="47"/>
+      <c r="G111" s="47">
+        <v>1</v>
+      </c>
+      <c r="H111" s="47"/>
+      <c r="I111" s="47">
+        <v>1</v>
+      </c>
+      <c r="J111" s="47"/>
+      <c r="K111" s="47">
         <f t="shared" si="18"/>
         <v>3</v>
       </c>
@@ -18908,17 +18951,17 @@
       <c r="D112" s="40" t="s">
         <v>331</v>
       </c>
-      <c r="E112" s="61"/>
-      <c r="F112" s="61">
-        <v>1</v>
-      </c>
-      <c r="G112" s="61"/>
-      <c r="H112" s="61">
-        <v>1</v>
-      </c>
-      <c r="I112" s="61"/>
-      <c r="J112" s="61"/>
-      <c r="K112" s="61">
+      <c r="E112" s="47"/>
+      <c r="F112" s="47">
+        <v>1</v>
+      </c>
+      <c r="G112" s="47"/>
+      <c r="H112" s="47">
+        <v>1</v>
+      </c>
+      <c r="I112" s="47"/>
+      <c r="J112" s="47"/>
+      <c r="K112" s="47">
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
@@ -18939,17 +18982,17 @@
       <c r="D113" s="40" t="s">
         <v>332</v>
       </c>
-      <c r="E113" s="61"/>
-      <c r="F113" s="61">
-        <v>1</v>
-      </c>
-      <c r="G113" s="61"/>
-      <c r="H113" s="61">
-        <v>1</v>
-      </c>
-      <c r="I113" s="61"/>
-      <c r="J113" s="61"/>
-      <c r="K113" s="61">
+      <c r="E113" s="47"/>
+      <c r="F113" s="47">
+        <v>1</v>
+      </c>
+      <c r="G113" s="47"/>
+      <c r="H113" s="47">
+        <v>1</v>
+      </c>
+      <c r="I113" s="47"/>
+      <c r="J113" s="47"/>
+      <c r="K113" s="47">
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
@@ -18970,21 +19013,21 @@
       <c r="D114" s="40" t="s">
         <v>333</v>
       </c>
-      <c r="E114" s="61">
-        <v>1</v>
-      </c>
-      <c r="F114" s="61"/>
-      <c r="G114" s="61">
-        <v>1</v>
-      </c>
-      <c r="H114" s="61"/>
-      <c r="I114" s="61">
-        <v>1</v>
-      </c>
-      <c r="J114" s="61">
-        <v>1</v>
-      </c>
-      <c r="K114" s="61">
+      <c r="E114" s="47">
+        <v>1</v>
+      </c>
+      <c r="F114" s="47"/>
+      <c r="G114" s="47">
+        <v>1</v>
+      </c>
+      <c r="H114" s="47"/>
+      <c r="I114" s="47">
+        <v>1</v>
+      </c>
+      <c r="J114" s="47">
+        <v>1</v>
+      </c>
+      <c r="K114" s="47">
         <f t="shared" si="18"/>
         <v>4</v>
       </c>
@@ -19005,17 +19048,17 @@
       <c r="D115" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="E115" s="61"/>
-      <c r="F115" s="61">
-        <v>1</v>
-      </c>
-      <c r="G115" s="61"/>
-      <c r="H115" s="61">
-        <v>1</v>
-      </c>
-      <c r="I115" s="61"/>
-      <c r="J115" s="61"/>
-      <c r="K115" s="61">
+      <c r="E115" s="47"/>
+      <c r="F115" s="47">
+        <v>1</v>
+      </c>
+      <c r="G115" s="47"/>
+      <c r="H115" s="47">
+        <v>1</v>
+      </c>
+      <c r="I115" s="47"/>
+      <c r="J115" s="47"/>
+      <c r="K115" s="47">
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
@@ -19038,31 +19081,31 @@
       <c r="L116" s="40"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E117" s="59">
+      <c r="E117" s="45">
         <f>SUM(E119:E130)</f>
         <v>5</v>
       </c>
-      <c r="F117" s="59">
+      <c r="F117" s="45">
         <f t="shared" ref="F117:J117" si="19">SUM(F119:F130)</f>
         <v>5</v>
       </c>
-      <c r="G117" s="59">
+      <c r="G117" s="45">
         <f t="shared" si="19"/>
         <v>5</v>
       </c>
-      <c r="H117" s="59">
+      <c r="H117" s="45">
         <f t="shared" si="19"/>
         <v>4</v>
       </c>
-      <c r="I117" s="59">
+      <c r="I117" s="45">
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="J117" s="59">
+      <c r="J117" s="45">
         <f t="shared" si="19"/>
         <v>2</v>
       </c>
-      <c r="K117" s="59"/>
+      <c r="K117" s="45"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="42" t="s">
@@ -19077,25 +19120,25 @@
       <c r="D118" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E118" s="60" t="s">
+      <c r="E118" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F118" s="60" t="s">
+      <c r="F118" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G118" s="60" t="s">
+      <c r="G118" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H118" s="60" t="s">
+      <c r="H118" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I118" s="60" t="s">
+      <c r="I118" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J118" s="60" t="s">
+      <c r="J118" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K118" s="60" t="s">
+      <c r="K118" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L118" s="16" t="s">
@@ -19115,17 +19158,17 @@
       <c r="D119" s="26" t="s">
         <v>335</v>
       </c>
-      <c r="E119" s="63">
-        <v>1</v>
-      </c>
-      <c r="F119" s="63"/>
-      <c r="G119" s="63"/>
-      <c r="H119" s="63"/>
-      <c r="I119" s="62">
+      <c r="E119" s="49">
+        <v>1</v>
+      </c>
+      <c r="F119" s="49"/>
+      <c r="G119" s="49"/>
+      <c r="H119" s="49"/>
+      <c r="I119" s="48">
         <v>0</v>
       </c>
-      <c r="J119" s="63"/>
-      <c r="K119" s="63">
+      <c r="J119" s="49"/>
+      <c r="K119" s="49">
         <f t="shared" ref="K119:K130" si="20">SUM(E119:J119)</f>
         <v>1</v>
       </c>
@@ -19146,17 +19189,17 @@
       <c r="D120" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="E120" s="63">
-        <v>1</v>
-      </c>
-      <c r="F120" s="63"/>
-      <c r="G120" s="63">
-        <v>1</v>
-      </c>
-      <c r="H120" s="63"/>
-      <c r="I120" s="63"/>
-      <c r="J120" s="63"/>
-      <c r="K120" s="63">
+      <c r="E120" s="49">
+        <v>1</v>
+      </c>
+      <c r="F120" s="49"/>
+      <c r="G120" s="49">
+        <v>1</v>
+      </c>
+      <c r="H120" s="49"/>
+      <c r="I120" s="49"/>
+      <c r="J120" s="49"/>
+      <c r="K120" s="49">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -19177,19 +19220,19 @@
       <c r="D121" s="40" t="s">
         <v>337</v>
       </c>
-      <c r="E121" s="61">
-        <v>1</v>
-      </c>
-      <c r="F121" s="61"/>
-      <c r="G121" s="61">
-        <v>1</v>
-      </c>
-      <c r="H121" s="61"/>
-      <c r="I121" s="61">
-        <v>1</v>
-      </c>
-      <c r="J121" s="61"/>
-      <c r="K121" s="61">
+      <c r="E121" s="47">
+        <v>1</v>
+      </c>
+      <c r="F121" s="47"/>
+      <c r="G121" s="47">
+        <v>1</v>
+      </c>
+      <c r="H121" s="47"/>
+      <c r="I121" s="47">
+        <v>1</v>
+      </c>
+      <c r="J121" s="47"/>
+      <c r="K121" s="47">
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
@@ -19210,19 +19253,19 @@
       <c r="D122" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="E122" s="61">
-        <v>1</v>
-      </c>
-      <c r="F122" s="61"/>
-      <c r="G122" s="61">
-        <v>1</v>
-      </c>
-      <c r="H122" s="61"/>
-      <c r="I122" s="61">
-        <v>1</v>
-      </c>
-      <c r="J122" s="61"/>
-      <c r="K122" s="61">
+      <c r="E122" s="47">
+        <v>1</v>
+      </c>
+      <c r="F122" s="47"/>
+      <c r="G122" s="47">
+        <v>1</v>
+      </c>
+      <c r="H122" s="47"/>
+      <c r="I122" s="47">
+        <v>1</v>
+      </c>
+      <c r="J122" s="47"/>
+      <c r="K122" s="47">
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
@@ -19243,15 +19286,15 @@
       <c r="D123" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="E123" s="63"/>
-      <c r="F123" s="63">
-        <v>1</v>
-      </c>
-      <c r="G123" s="63"/>
-      <c r="H123" s="63"/>
-      <c r="I123" s="63"/>
-      <c r="J123" s="63"/>
-      <c r="K123" s="63">
+      <c r="E123" s="49"/>
+      <c r="F123" s="49">
+        <v>1</v>
+      </c>
+      <c r="G123" s="49"/>
+      <c r="H123" s="49"/>
+      <c r="I123" s="49"/>
+      <c r="J123" s="49"/>
+      <c r="K123" s="49">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -19272,19 +19315,19 @@
       <c r="D124" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="E124" s="61">
-        <v>1</v>
-      </c>
-      <c r="F124" s="61"/>
-      <c r="G124" s="61">
-        <v>1</v>
-      </c>
-      <c r="H124" s="61"/>
-      <c r="I124" s="61">
-        <v>1</v>
-      </c>
-      <c r="J124" s="61"/>
-      <c r="K124" s="61">
+      <c r="E124" s="47">
+        <v>1</v>
+      </c>
+      <c r="F124" s="47"/>
+      <c r="G124" s="47">
+        <v>1</v>
+      </c>
+      <c r="H124" s="47"/>
+      <c r="I124" s="47">
+        <v>1</v>
+      </c>
+      <c r="J124" s="47"/>
+      <c r="K124" s="47">
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
@@ -19305,15 +19348,15 @@
       <c r="D125" s="26" t="s">
         <v>341</v>
       </c>
-      <c r="E125" s="63"/>
-      <c r="F125" s="63"/>
-      <c r="G125" s="63">
-        <v>1</v>
-      </c>
-      <c r="H125" s="63"/>
-      <c r="I125" s="63"/>
-      <c r="J125" s="63"/>
-      <c r="K125" s="63">
+      <c r="E125" s="49"/>
+      <c r="F125" s="49"/>
+      <c r="G125" s="49">
+        <v>1</v>
+      </c>
+      <c r="H125" s="49"/>
+      <c r="I125" s="49"/>
+      <c r="J125" s="49"/>
+      <c r="K125" s="49">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -19334,17 +19377,17 @@
       <c r="D126" s="26" t="s">
         <v>342</v>
       </c>
-      <c r="E126" s="63"/>
-      <c r="F126" s="63">
-        <v>1</v>
-      </c>
-      <c r="G126" s="63"/>
-      <c r="H126" s="62">
+      <c r="E126" s="49"/>
+      <c r="F126" s="49">
+        <v>1</v>
+      </c>
+      <c r="G126" s="49"/>
+      <c r="H126" s="48">
         <v>0</v>
       </c>
-      <c r="I126" s="63"/>
-      <c r="J126" s="63"/>
-      <c r="K126" s="63">
+      <c r="I126" s="49"/>
+      <c r="J126" s="49"/>
+      <c r="K126" s="49">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -19365,15 +19408,15 @@
       <c r="D127" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="E127" s="63"/>
-      <c r="F127" s="63"/>
-      <c r="G127" s="63"/>
-      <c r="H127" s="63">
-        <v>1</v>
-      </c>
-      <c r="I127" s="63"/>
-      <c r="J127" s="63"/>
-      <c r="K127" s="63">
+      <c r="E127" s="49"/>
+      <c r="F127" s="49"/>
+      <c r="G127" s="49"/>
+      <c r="H127" s="49">
+        <v>1</v>
+      </c>
+      <c r="I127" s="49"/>
+      <c r="J127" s="49"/>
+      <c r="K127" s="49">
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
@@ -19394,19 +19437,19 @@
       <c r="D128" s="40" t="s">
         <v>344</v>
       </c>
-      <c r="E128" s="61"/>
-      <c r="F128" s="61">
-        <v>1</v>
-      </c>
-      <c r="G128" s="61"/>
-      <c r="H128" s="61">
-        <v>1</v>
-      </c>
-      <c r="I128" s="61"/>
-      <c r="J128" s="61">
-        <v>1</v>
-      </c>
-      <c r="K128" s="61">
+      <c r="E128" s="47"/>
+      <c r="F128" s="47">
+        <v>1</v>
+      </c>
+      <c r="G128" s="47"/>
+      <c r="H128" s="47">
+        <v>1</v>
+      </c>
+      <c r="I128" s="47"/>
+      <c r="J128" s="47">
+        <v>1</v>
+      </c>
+      <c r="K128" s="47">
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
@@ -19427,19 +19470,19 @@
       <c r="D129" s="40" t="s">
         <v>345</v>
       </c>
-      <c r="E129" s="61"/>
-      <c r="F129" s="61">
-        <v>1</v>
-      </c>
-      <c r="G129" s="61"/>
-      <c r="H129" s="61">
-        <v>1</v>
-      </c>
-      <c r="I129" s="61"/>
-      <c r="J129" s="61">
-        <v>1</v>
-      </c>
-      <c r="K129" s="61">
+      <c r="E129" s="47"/>
+      <c r="F129" s="47">
+        <v>1</v>
+      </c>
+      <c r="G129" s="47"/>
+      <c r="H129" s="47">
+        <v>1</v>
+      </c>
+      <c r="I129" s="47"/>
+      <c r="J129" s="47">
+        <v>1</v>
+      </c>
+      <c r="K129" s="47">
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
@@ -19460,17 +19503,17 @@
       <c r="D130" s="40" t="s">
         <v>346</v>
       </c>
-      <c r="E130" s="61"/>
-      <c r="F130" s="61">
-        <v>1</v>
-      </c>
-      <c r="G130" s="61"/>
-      <c r="H130" s="61">
-        <v>1</v>
-      </c>
-      <c r="I130" s="61"/>
-      <c r="J130" s="61"/>
-      <c r="K130" s="61">
+      <c r="E130" s="47"/>
+      <c r="F130" s="47">
+        <v>1</v>
+      </c>
+      <c r="G130" s="47"/>
+      <c r="H130" s="47">
+        <v>1</v>
+      </c>
+      <c r="I130" s="47"/>
+      <c r="J130" s="47"/>
+      <c r="K130" s="47">
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
@@ -19569,17 +19612,17 @@
       <c r="D134" s="40" t="s">
         <v>347</v>
       </c>
-      <c r="E134" s="61"/>
-      <c r="F134" s="61">
-        <v>1</v>
-      </c>
-      <c r="G134" s="61"/>
-      <c r="H134" s="61">
-        <v>1</v>
-      </c>
-      <c r="I134" s="61"/>
-      <c r="J134" s="61"/>
-      <c r="K134" s="61">
+      <c r="E134" s="47"/>
+      <c r="F134" s="47">
+        <v>1</v>
+      </c>
+      <c r="G134" s="47"/>
+      <c r="H134" s="47">
+        <v>1</v>
+      </c>
+      <c r="I134" s="47"/>
+      <c r="J134" s="47"/>
+      <c r="K134" s="47">
         <f t="shared" ref="K134:K142" si="22">SUM(E134:J134)</f>
         <v>2</v>
       </c>
@@ -19600,15 +19643,15 @@
       <c r="D135" s="40" t="s">
         <v>348</v>
       </c>
-      <c r="E135" s="61"/>
-      <c r="F135" s="61"/>
-      <c r="G135" s="61"/>
-      <c r="H135" s="61">
-        <v>1</v>
-      </c>
-      <c r="I135" s="61"/>
-      <c r="J135" s="61"/>
-      <c r="K135" s="61">
+      <c r="E135" s="47"/>
+      <c r="F135" s="47"/>
+      <c r="G135" s="47"/>
+      <c r="H135" s="47">
+        <v>1</v>
+      </c>
+      <c r="I135" s="47"/>
+      <c r="J135" s="47"/>
+      <c r="K135" s="47">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
@@ -19629,19 +19672,19 @@
       <c r="D136" s="40" t="s">
         <v>349</v>
       </c>
-      <c r="E136" s="61">
-        <v>1</v>
-      </c>
-      <c r="F136" s="61"/>
-      <c r="G136" s="61">
-        <v>1</v>
-      </c>
-      <c r="H136" s="61"/>
-      <c r="I136" s="61">
-        <v>1</v>
-      </c>
-      <c r="J136" s="61"/>
-      <c r="K136" s="61">
+      <c r="E136" s="47">
+        <v>1</v>
+      </c>
+      <c r="F136" s="47"/>
+      <c r="G136" s="47">
+        <v>1</v>
+      </c>
+      <c r="H136" s="47"/>
+      <c r="I136" s="47">
+        <v>1</v>
+      </c>
+      <c r="J136" s="47"/>
+      <c r="K136" s="47">
         <f t="shared" si="22"/>
         <v>3</v>
       </c>
@@ -19662,17 +19705,17 @@
       <c r="D137" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="E137" s="63"/>
-      <c r="F137" s="63">
-        <v>1</v>
-      </c>
-      <c r="G137" s="63"/>
-      <c r="H137" s="63"/>
-      <c r="I137" s="62">
+      <c r="E137" s="49"/>
+      <c r="F137" s="49">
+        <v>1</v>
+      </c>
+      <c r="G137" s="49"/>
+      <c r="H137" s="49"/>
+      <c r="I137" s="48">
         <v>0</v>
       </c>
-      <c r="J137" s="63"/>
-      <c r="K137" s="63">
+      <c r="J137" s="49"/>
+      <c r="K137" s="49">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
@@ -19693,17 +19736,17 @@
       <c r="D138" s="26" t="s">
         <v>351</v>
       </c>
-      <c r="E138" s="63">
-        <v>1</v>
-      </c>
-      <c r="F138" s="63"/>
-      <c r="G138" s="62">
+      <c r="E138" s="49">
+        <v>1</v>
+      </c>
+      <c r="F138" s="49"/>
+      <c r="G138" s="48">
         <v>0</v>
       </c>
-      <c r="H138" s="63"/>
-      <c r="I138" s="63"/>
-      <c r="J138" s="63"/>
-      <c r="K138" s="63">
+      <c r="H138" s="49"/>
+      <c r="I138" s="49"/>
+      <c r="J138" s="49"/>
+      <c r="K138" s="49">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
@@ -19724,17 +19767,17 @@
       <c r="D139" s="40" t="s">
         <v>352</v>
       </c>
-      <c r="E139" s="61"/>
-      <c r="F139" s="61">
-        <v>1</v>
-      </c>
-      <c r="G139" s="61"/>
-      <c r="H139" s="61">
-        <v>1</v>
-      </c>
-      <c r="I139" s="61"/>
-      <c r="J139" s="61"/>
-      <c r="K139" s="61">
+      <c r="E139" s="47"/>
+      <c r="F139" s="47">
+        <v>1</v>
+      </c>
+      <c r="G139" s="47"/>
+      <c r="H139" s="47">
+        <v>1</v>
+      </c>
+      <c r="I139" s="47"/>
+      <c r="J139" s="47"/>
+      <c r="K139" s="47">
         <f t="shared" si="22"/>
         <v>2</v>
       </c>
@@ -19755,21 +19798,21 @@
       <c r="D140" s="40" t="s">
         <v>353</v>
       </c>
-      <c r="E140" s="61">
-        <v>1</v>
-      </c>
-      <c r="F140" s="61"/>
-      <c r="G140" s="61">
-        <v>1</v>
-      </c>
-      <c r="H140" s="61"/>
-      <c r="I140" s="61">
-        <v>1</v>
-      </c>
-      <c r="J140" s="61">
-        <v>1</v>
-      </c>
-      <c r="K140" s="61">
+      <c r="E140" s="47">
+        <v>1</v>
+      </c>
+      <c r="F140" s="47"/>
+      <c r="G140" s="47">
+        <v>1</v>
+      </c>
+      <c r="H140" s="47"/>
+      <c r="I140" s="47">
+        <v>1</v>
+      </c>
+      <c r="J140" s="47">
+        <v>1</v>
+      </c>
+      <c r="K140" s="47">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
@@ -19790,21 +19833,21 @@
       <c r="D141" s="40" t="s">
         <v>354</v>
       </c>
-      <c r="E141" s="61">
-        <v>1</v>
-      </c>
-      <c r="F141" s="61"/>
-      <c r="G141" s="61">
-        <v>1</v>
-      </c>
-      <c r="H141" s="61"/>
-      <c r="I141" s="61">
-        <v>1</v>
-      </c>
-      <c r="J141" s="61">
-        <v>1</v>
-      </c>
-      <c r="K141" s="61">
+      <c r="E141" s="47">
+        <v>1</v>
+      </c>
+      <c r="F141" s="47"/>
+      <c r="G141" s="47">
+        <v>1</v>
+      </c>
+      <c r="H141" s="47"/>
+      <c r="I141" s="47">
+        <v>1</v>
+      </c>
+      <c r="J141" s="47">
+        <v>1</v>
+      </c>
+      <c r="K141" s="47">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
@@ -19825,17 +19868,17 @@
       <c r="D142" s="40" t="s">
         <v>355</v>
       </c>
-      <c r="E142" s="61"/>
-      <c r="F142" s="61">
-        <v>1</v>
-      </c>
-      <c r="G142" s="61"/>
-      <c r="H142" s="61">
-        <v>1</v>
-      </c>
-      <c r="I142" s="61"/>
-      <c r="J142" s="61"/>
-      <c r="K142" s="61">
+      <c r="E142" s="47"/>
+      <c r="F142" s="47">
+        <v>1</v>
+      </c>
+      <c r="G142" s="47"/>
+      <c r="H142" s="47">
+        <v>1</v>
+      </c>
+      <c r="I142" s="47"/>
+      <c r="J142" s="47"/>
+      <c r="K142" s="47">
         <f t="shared" si="22"/>
         <v>2</v>
       </c>
@@ -19858,31 +19901,31 @@
       <c r="L143" s="40"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E144" s="59">
+      <c r="E144" s="45">
         <f>SUM(E146:E150)</f>
         <v>3</v>
       </c>
-      <c r="F144" s="59">
+      <c r="F144" s="45">
         <f t="shared" ref="F144:J144" si="23">SUM(F146:F150)</f>
         <v>3</v>
       </c>
-      <c r="G144" s="59">
+      <c r="G144" s="45">
         <f t="shared" si="23"/>
         <v>3</v>
       </c>
-      <c r="H144" s="59">
+      <c r="H144" s="45">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
-      <c r="I144" s="59">
+      <c r="I144" s="45">
         <f t="shared" si="23"/>
         <v>3</v>
       </c>
-      <c r="J144" s="59">
+      <c r="J144" s="45">
         <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="K144" s="59"/>
+      <c r="K144" s="45"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="42" t="s">
@@ -19897,25 +19940,25 @@
       <c r="D145" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E145" s="60" t="s">
+      <c r="E145" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F145" s="60" t="s">
+      <c r="F145" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G145" s="60" t="s">
+      <c r="G145" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H145" s="60" t="s">
+      <c r="H145" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I145" s="60" t="s">
+      <c r="I145" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J145" s="60" t="s">
+      <c r="J145" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K145" s="60" t="s">
+      <c r="K145" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L145" s="16" t="s">
@@ -19935,19 +19978,19 @@
       <c r="D146" s="40" t="s">
         <v>356</v>
       </c>
-      <c r="E146" s="61">
-        <v>1</v>
-      </c>
-      <c r="F146" s="61"/>
-      <c r="G146" s="61">
-        <v>1</v>
-      </c>
-      <c r="H146" s="61"/>
-      <c r="I146" s="61">
-        <v>1</v>
-      </c>
-      <c r="J146" s="61"/>
-      <c r="K146" s="61">
+      <c r="E146" s="47">
+        <v>1</v>
+      </c>
+      <c r="F146" s="47"/>
+      <c r="G146" s="47">
+        <v>1</v>
+      </c>
+      <c r="H146" s="47"/>
+      <c r="I146" s="47">
+        <v>1</v>
+      </c>
+      <c r="J146" s="47"/>
+      <c r="K146" s="47">
         <f t="shared" ref="K146:K150" si="24">SUM(E146:J146)</f>
         <v>3</v>
       </c>
@@ -19968,19 +20011,19 @@
       <c r="D147" s="40" t="s">
         <v>357</v>
       </c>
-      <c r="E147" s="61">
-        <v>1</v>
-      </c>
-      <c r="F147" s="61"/>
-      <c r="G147" s="61">
-        <v>1</v>
-      </c>
-      <c r="H147" s="61"/>
-      <c r="I147" s="61">
-        <v>1</v>
-      </c>
-      <c r="J147" s="61"/>
-      <c r="K147" s="61">
+      <c r="E147" s="47">
+        <v>1</v>
+      </c>
+      <c r="F147" s="47"/>
+      <c r="G147" s="47">
+        <v>1</v>
+      </c>
+      <c r="H147" s="47"/>
+      <c r="I147" s="47">
+        <v>1</v>
+      </c>
+      <c r="J147" s="47"/>
+      <c r="K147" s="47">
         <f t="shared" si="24"/>
         <v>3</v>
       </c>
@@ -20001,17 +20044,17 @@
       <c r="D148" s="40" t="s">
         <v>358</v>
       </c>
-      <c r="E148" s="61"/>
-      <c r="F148" s="61">
-        <v>1</v>
-      </c>
-      <c r="G148" s="61"/>
-      <c r="H148" s="61">
-        <v>1</v>
-      </c>
-      <c r="I148" s="61"/>
-      <c r="J148" s="61"/>
-      <c r="K148" s="61">
+      <c r="E148" s="47"/>
+      <c r="F148" s="47">
+        <v>1</v>
+      </c>
+      <c r="G148" s="47"/>
+      <c r="H148" s="47">
+        <v>1</v>
+      </c>
+      <c r="I148" s="47"/>
+      <c r="J148" s="47"/>
+      <c r="K148" s="47">
         <f t="shared" si="24"/>
         <v>2</v>
       </c>
@@ -20032,17 +20075,17 @@
       <c r="D149" s="26" t="s">
         <v>359</v>
       </c>
-      <c r="E149" s="63"/>
-      <c r="F149" s="63">
-        <v>1</v>
-      </c>
-      <c r="G149" s="63"/>
-      <c r="H149" s="62">
+      <c r="E149" s="49"/>
+      <c r="F149" s="49">
+        <v>1</v>
+      </c>
+      <c r="G149" s="49"/>
+      <c r="H149" s="48">
         <v>0</v>
       </c>
-      <c r="I149" s="63"/>
-      <c r="J149" s="63"/>
-      <c r="K149" s="63">
+      <c r="I149" s="49"/>
+      <c r="J149" s="49"/>
+      <c r="K149" s="49">
         <f t="shared" si="24"/>
         <v>1</v>
       </c>
@@ -20063,25 +20106,25 @@
       <c r="D150" s="40" t="s">
         <v>360</v>
       </c>
-      <c r="E150" s="61">
-        <v>1</v>
-      </c>
-      <c r="F150" s="61">
-        <v>1</v>
-      </c>
-      <c r="G150" s="61">
-        <v>1</v>
-      </c>
-      <c r="H150" s="61">
-        <v>1</v>
-      </c>
-      <c r="I150" s="61">
-        <v>1</v>
-      </c>
-      <c r="J150" s="61">
-        <v>1</v>
-      </c>
-      <c r="K150" s="61">
+      <c r="E150" s="47">
+        <v>1</v>
+      </c>
+      <c r="F150" s="47">
+        <v>1</v>
+      </c>
+      <c r="G150" s="47">
+        <v>1</v>
+      </c>
+      <c r="H150" s="47">
+        <v>1</v>
+      </c>
+      <c r="I150" s="47">
+        <v>1</v>
+      </c>
+      <c r="J150" s="47">
+        <v>1</v>
+      </c>
+      <c r="K150" s="47">
         <f t="shared" si="24"/>
         <v>6</v>
       </c>
@@ -20104,31 +20147,31 @@
       <c r="L151" s="40"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E152" s="59">
+      <c r="E152" s="45">
         <f>SUM(E154:E163)</f>
         <v>3</v>
       </c>
-      <c r="F152" s="59">
+      <c r="F152" s="45">
         <f t="shared" ref="F152:J152" si="25">SUM(F154:F163)</f>
         <v>4</v>
       </c>
-      <c r="G152" s="59">
+      <c r="G152" s="45">
         <f t="shared" si="25"/>
         <v>3</v>
       </c>
-      <c r="H152" s="59">
+      <c r="H152" s="45">
         <f t="shared" si="25"/>
         <v>5</v>
       </c>
-      <c r="I152" s="59">
+      <c r="I152" s="45">
         <f t="shared" si="25"/>
         <v>4</v>
       </c>
-      <c r="J152" s="59">
+      <c r="J152" s="45">
         <f t="shared" si="25"/>
         <v>2</v>
       </c>
-      <c r="K152" s="59"/>
+      <c r="K152" s="45"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="42" t="s">
@@ -20143,25 +20186,25 @@
       <c r="D153" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E153" s="60" t="s">
+      <c r="E153" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F153" s="60" t="s">
+      <c r="F153" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G153" s="60" t="s">
+      <c r="G153" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H153" s="60" t="s">
+      <c r="H153" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I153" s="60" t="s">
+      <c r="I153" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J153" s="60" t="s">
+      <c r="J153" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K153" s="60" t="s">
+      <c r="K153" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L153" s="16" t="s">
@@ -20181,17 +20224,17 @@
       <c r="D154" s="40" t="s">
         <v>361</v>
       </c>
-      <c r="E154" s="61"/>
-      <c r="F154" s="61">
-        <v>1</v>
-      </c>
-      <c r="G154" s="61"/>
-      <c r="H154" s="61">
-        <v>1</v>
-      </c>
-      <c r="I154" s="61"/>
-      <c r="J154" s="61"/>
-      <c r="K154" s="61">
+      <c r="E154" s="47"/>
+      <c r="F154" s="47">
+        <v>1</v>
+      </c>
+      <c r="G154" s="47"/>
+      <c r="H154" s="47">
+        <v>1</v>
+      </c>
+      <c r="I154" s="47"/>
+      <c r="J154" s="47"/>
+      <c r="K154" s="47">
         <f t="shared" ref="K154:K163" si="26">SUM(E154:J154)</f>
         <v>2</v>
       </c>
@@ -20212,15 +20255,15 @@
       <c r="D155" s="26" t="s">
         <v>362</v>
       </c>
-      <c r="E155" s="63"/>
-      <c r="F155" s="63"/>
-      <c r="G155" s="63">
-        <v>1</v>
-      </c>
-      <c r="H155" s="63"/>
-      <c r="I155" s="63"/>
-      <c r="J155" s="63"/>
-      <c r="K155" s="63">
+      <c r="E155" s="49"/>
+      <c r="F155" s="49"/>
+      <c r="G155" s="49">
+        <v>1</v>
+      </c>
+      <c r="H155" s="49"/>
+      <c r="I155" s="49"/>
+      <c r="J155" s="49"/>
+      <c r="K155" s="49">
         <f t="shared" si="26"/>
         <v>1</v>
       </c>
@@ -20241,19 +20284,19 @@
       <c r="D156" s="40" t="s">
         <v>363</v>
       </c>
-      <c r="E156" s="61"/>
-      <c r="F156" s="61">
-        <v>1</v>
-      </c>
-      <c r="G156" s="61"/>
-      <c r="H156" s="61">
-        <v>1</v>
-      </c>
-      <c r="I156" s="61"/>
-      <c r="J156" s="61">
-        <v>1</v>
-      </c>
-      <c r="K156" s="61">
+      <c r="E156" s="47"/>
+      <c r="F156" s="47">
+        <v>1</v>
+      </c>
+      <c r="G156" s="47"/>
+      <c r="H156" s="47">
+        <v>1</v>
+      </c>
+      <c r="I156" s="47"/>
+      <c r="J156" s="47">
+        <v>1</v>
+      </c>
+      <c r="K156" s="47">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
@@ -20274,19 +20317,19 @@
       <c r="D157" s="40" t="s">
         <v>364</v>
       </c>
-      <c r="E157" s="61"/>
-      <c r="F157" s="61">
-        <v>1</v>
-      </c>
-      <c r="G157" s="61"/>
-      <c r="H157" s="61">
-        <v>1</v>
-      </c>
-      <c r="I157" s="61"/>
-      <c r="J157" s="61">
-        <v>1</v>
-      </c>
-      <c r="K157" s="61">
+      <c r="E157" s="47"/>
+      <c r="F157" s="47">
+        <v>1</v>
+      </c>
+      <c r="G157" s="47"/>
+      <c r="H157" s="47">
+        <v>1</v>
+      </c>
+      <c r="I157" s="47"/>
+      <c r="J157" s="47">
+        <v>1</v>
+      </c>
+      <c r="K157" s="47">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
@@ -20307,19 +20350,19 @@
       <c r="D158" s="40" t="s">
         <v>367</v>
       </c>
-      <c r="E158" s="61">
-        <v>1</v>
-      </c>
-      <c r="F158" s="61"/>
-      <c r="G158" s="61">
-        <v>1</v>
-      </c>
-      <c r="H158" s="61"/>
-      <c r="I158" s="61">
-        <v>1</v>
-      </c>
-      <c r="J158" s="61"/>
-      <c r="K158" s="61">
+      <c r="E158" s="47">
+        <v>1</v>
+      </c>
+      <c r="F158" s="47"/>
+      <c r="G158" s="47">
+        <v>1</v>
+      </c>
+      <c r="H158" s="47"/>
+      <c r="I158" s="47">
+        <v>1</v>
+      </c>
+      <c r="J158" s="47"/>
+      <c r="K158" s="47">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
@@ -20340,19 +20383,19 @@
       <c r="D159" s="40" t="s">
         <v>368</v>
       </c>
-      <c r="E159" s="61"/>
-      <c r="F159" s="61">
-        <v>1</v>
-      </c>
-      <c r="G159" s="61"/>
-      <c r="H159" s="61">
-        <v>1</v>
-      </c>
-      <c r="I159" s="61">
-        <v>1</v>
-      </c>
-      <c r="J159" s="61"/>
-      <c r="K159" s="61">
+      <c r="E159" s="47"/>
+      <c r="F159" s="47">
+        <v>1</v>
+      </c>
+      <c r="G159" s="47"/>
+      <c r="H159" s="47">
+        <v>1</v>
+      </c>
+      <c r="I159" s="47">
+        <v>1</v>
+      </c>
+      <c r="J159" s="47"/>
+      <c r="K159" s="47">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
@@ -20373,17 +20416,17 @@
       <c r="D160" s="26" t="s">
         <v>369</v>
       </c>
-      <c r="E160" s="63">
-        <v>1</v>
-      </c>
-      <c r="F160" s="63"/>
-      <c r="G160" s="62">
+      <c r="E160" s="49">
+        <v>1</v>
+      </c>
+      <c r="F160" s="49"/>
+      <c r="G160" s="48">
         <v>0</v>
       </c>
-      <c r="H160" s="63"/>
-      <c r="I160" s="63"/>
-      <c r="J160" s="63"/>
-      <c r="K160" s="63">
+      <c r="H160" s="49"/>
+      <c r="I160" s="49"/>
+      <c r="J160" s="49"/>
+      <c r="K160" s="49">
         <f t="shared" si="26"/>
         <v>1</v>
       </c>
@@ -20404,15 +20447,15 @@
       <c r="D161" s="26" t="s">
         <v>370</v>
       </c>
-      <c r="E161" s="63"/>
-      <c r="F161" s="63"/>
-      <c r="G161" s="63"/>
-      <c r="H161" s="63"/>
-      <c r="I161" s="63">
-        <v>1</v>
-      </c>
-      <c r="J161" s="63"/>
-      <c r="K161" s="63">
+      <c r="E161" s="49"/>
+      <c r="F161" s="49"/>
+      <c r="G161" s="49"/>
+      <c r="H161" s="49"/>
+      <c r="I161" s="49">
+        <v>1</v>
+      </c>
+      <c r="J161" s="49"/>
+      <c r="K161" s="49">
         <f t="shared" si="26"/>
         <v>1</v>
       </c>
@@ -20433,15 +20476,15 @@
       <c r="D162" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E162" s="63"/>
-      <c r="F162" s="63"/>
-      <c r="G162" s="63"/>
-      <c r="H162" s="63">
-        <v>1</v>
-      </c>
-      <c r="I162" s="63"/>
-      <c r="J162" s="63"/>
-      <c r="K162" s="63">
+      <c r="E162" s="49"/>
+      <c r="F162" s="49"/>
+      <c r="G162" s="49"/>
+      <c r="H162" s="49">
+        <v>1</v>
+      </c>
+      <c r="I162" s="49"/>
+      <c r="J162" s="49"/>
+      <c r="K162" s="49">
         <f t="shared" si="26"/>
         <v>1</v>
       </c>
@@ -20462,19 +20505,19 @@
       <c r="D163" s="40" t="s">
         <v>372</v>
       </c>
-      <c r="E163" s="61">
-        <v>1</v>
-      </c>
-      <c r="F163" s="61"/>
-      <c r="G163" s="61">
-        <v>1</v>
-      </c>
-      <c r="H163" s="61"/>
-      <c r="I163" s="61">
-        <v>1</v>
-      </c>
-      <c r="J163" s="61"/>
-      <c r="K163" s="61">
+      <c r="E163" s="47">
+        <v>1</v>
+      </c>
+      <c r="F163" s="47"/>
+      <c r="G163" s="47">
+        <v>1</v>
+      </c>
+      <c r="H163" s="47"/>
+      <c r="I163" s="47">
+        <v>1</v>
+      </c>
+      <c r="J163" s="47"/>
+      <c r="K163" s="47">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
@@ -20497,31 +20540,31 @@
       <c r="L164" s="40"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E165" s="59">
+      <c r="E165" s="45">
         <f>SUM(E167:E176)</f>
         <v>4</v>
       </c>
-      <c r="F165" s="59">
+      <c r="F165" s="45">
         <f t="shared" ref="F165:J165" si="27">SUM(F167:F176)</f>
         <v>4</v>
       </c>
-      <c r="G165" s="59">
+      <c r="G165" s="45">
         <f t="shared" si="27"/>
         <v>4</v>
       </c>
-      <c r="H165" s="59">
+      <c r="H165" s="45">
         <f t="shared" si="27"/>
         <v>4</v>
       </c>
-      <c r="I165" s="59">
+      <c r="I165" s="45">
         <f t="shared" si="27"/>
         <v>4</v>
       </c>
-      <c r="J165" s="59">
+      <c r="J165" s="45">
         <f t="shared" si="27"/>
         <v>1</v>
       </c>
-      <c r="K165" s="59"/>
+      <c r="K165" s="45"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="42" t="s">
@@ -20536,25 +20579,25 @@
       <c r="D166" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="E166" s="60" t="s">
+      <c r="E166" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="F166" s="60" t="s">
+      <c r="F166" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G166" s="60" t="s">
+      <c r="G166" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="H166" s="60" t="s">
+      <c r="H166" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="I166" s="60" t="s">
+      <c r="I166" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J166" s="60" t="s">
+      <c r="J166" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K166" s="60" t="s">
+      <c r="K166" s="46" t="s">
         <v>366</v>
       </c>
       <c r="L166" s="16" t="s">
@@ -20574,21 +20617,21 @@
       <c r="D167" s="40" t="s">
         <v>365</v>
       </c>
-      <c r="E167" s="61">
-        <v>1</v>
-      </c>
-      <c r="F167" s="61"/>
-      <c r="G167" s="61">
-        <v>1</v>
-      </c>
-      <c r="H167" s="61"/>
-      <c r="I167" s="61">
-        <v>1</v>
-      </c>
-      <c r="J167" s="61">
-        <v>1</v>
-      </c>
-      <c r="K167" s="61">
+      <c r="E167" s="47">
+        <v>1</v>
+      </c>
+      <c r="F167" s="47"/>
+      <c r="G167" s="47">
+        <v>1</v>
+      </c>
+      <c r="H167" s="47"/>
+      <c r="I167" s="47">
+        <v>1</v>
+      </c>
+      <c r="J167" s="47">
+        <v>1</v>
+      </c>
+      <c r="K167" s="47">
         <f t="shared" ref="K167:K176" si="28">SUM(E167:J167)</f>
         <v>4</v>
       </c>
@@ -20609,19 +20652,19 @@
       <c r="D168" s="40" t="s">
         <v>373</v>
       </c>
-      <c r="E168" s="61">
-        <v>1</v>
-      </c>
-      <c r="F168" s="61"/>
-      <c r="G168" s="61">
-        <v>1</v>
-      </c>
-      <c r="H168" s="61"/>
-      <c r="I168" s="61">
-        <v>1</v>
-      </c>
-      <c r="J168" s="61"/>
-      <c r="K168" s="61">
+      <c r="E168" s="47">
+        <v>1</v>
+      </c>
+      <c r="F168" s="47"/>
+      <c r="G168" s="47">
+        <v>1</v>
+      </c>
+      <c r="H168" s="47"/>
+      <c r="I168" s="47">
+        <v>1</v>
+      </c>
+      <c r="J168" s="47"/>
+      <c r="K168" s="47">
         <f t="shared" si="28"/>
         <v>3</v>
       </c>
@@ -20642,15 +20685,15 @@
       <c r="D169" s="26" t="s">
         <v>374</v>
       </c>
-      <c r="E169" s="63"/>
-      <c r="F169" s="63"/>
-      <c r="G169" s="63"/>
-      <c r="H169" s="63"/>
-      <c r="I169" s="63">
-        <v>1</v>
-      </c>
-      <c r="J169" s="63"/>
-      <c r="K169" s="63">
+      <c r="E169" s="49"/>
+      <c r="F169" s="49"/>
+      <c r="G169" s="49"/>
+      <c r="H169" s="49"/>
+      <c r="I169" s="49">
+        <v>1</v>
+      </c>
+      <c r="J169" s="49"/>
+      <c r="K169" s="49">
         <f t="shared" si="28"/>
         <v>1</v>
       </c>
@@ -20671,15 +20714,15 @@
       <c r="D170" s="26" t="s">
         <v>375</v>
       </c>
-      <c r="E170" s="63">
-        <v>1</v>
-      </c>
-      <c r="F170" s="63"/>
-      <c r="G170" s="63"/>
-      <c r="H170" s="63"/>
-      <c r="I170" s="63"/>
-      <c r="J170" s="63"/>
-      <c r="K170" s="63">
+      <c r="E170" s="49">
+        <v>1</v>
+      </c>
+      <c r="F170" s="49"/>
+      <c r="G170" s="49"/>
+      <c r="H170" s="49"/>
+      <c r="I170" s="49"/>
+      <c r="J170" s="49"/>
+      <c r="K170" s="49">
         <f t="shared" si="28"/>
         <v>1</v>
       </c>
@@ -20700,17 +20743,17 @@
       <c r="D171" s="26" t="s">
         <v>376</v>
       </c>
-      <c r="E171" s="63"/>
-      <c r="F171" s="63"/>
-      <c r="G171" s="63">
-        <v>1</v>
-      </c>
-      <c r="H171" s="63"/>
-      <c r="I171" s="63"/>
-      <c r="J171" s="62">
+      <c r="E171" s="49"/>
+      <c r="F171" s="49"/>
+      <c r="G171" s="49">
+        <v>1</v>
+      </c>
+      <c r="H171" s="49"/>
+      <c r="I171" s="49"/>
+      <c r="J171" s="48">
         <v>0</v>
       </c>
-      <c r="K171" s="63">
+      <c r="K171" s="49">
         <f t="shared" si="28"/>
         <v>1</v>
       </c>
@@ -20731,17 +20774,17 @@
       <c r="D172" s="40" t="s">
         <v>377</v>
       </c>
-      <c r="E172" s="61"/>
-      <c r="F172" s="61">
-        <v>1</v>
-      </c>
-      <c r="G172" s="61"/>
-      <c r="H172" s="61">
-        <v>1</v>
-      </c>
-      <c r="I172" s="61"/>
-      <c r="J172" s="61"/>
-      <c r="K172" s="61">
+      <c r="E172" s="47"/>
+      <c r="F172" s="47">
+        <v>1</v>
+      </c>
+      <c r="G172" s="47"/>
+      <c r="H172" s="47">
+        <v>1</v>
+      </c>
+      <c r="I172" s="47"/>
+      <c r="J172" s="47"/>
+      <c r="K172" s="47">
         <f t="shared" si="28"/>
         <v>2</v>
       </c>
@@ -20762,19 +20805,19 @@
       <c r="D173" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="E173" s="61">
-        <v>1</v>
-      </c>
-      <c r="F173" s="61"/>
-      <c r="G173" s="61">
-        <v>1</v>
-      </c>
-      <c r="H173" s="61"/>
-      <c r="I173" s="61">
-        <v>1</v>
-      </c>
-      <c r="J173" s="61"/>
-      <c r="K173" s="61">
+      <c r="E173" s="47">
+        <v>1</v>
+      </c>
+      <c r="F173" s="47"/>
+      <c r="G173" s="47">
+        <v>1</v>
+      </c>
+      <c r="H173" s="47"/>
+      <c r="I173" s="47">
+        <v>1</v>
+      </c>
+      <c r="J173" s="47"/>
+      <c r="K173" s="47">
         <f t="shared" si="28"/>
         <v>3</v>
       </c>
@@ -20795,17 +20838,17 @@
       <c r="D174" s="40" t="s">
         <v>379</v>
       </c>
-      <c r="E174" s="61"/>
-      <c r="F174" s="61">
-        <v>1</v>
-      </c>
-      <c r="G174" s="61"/>
-      <c r="H174" s="61">
-        <v>1</v>
-      </c>
-      <c r="I174" s="61"/>
-      <c r="J174" s="61"/>
-      <c r="K174" s="61">
+      <c r="E174" s="47"/>
+      <c r="F174" s="47">
+        <v>1</v>
+      </c>
+      <c r="G174" s="47"/>
+      <c r="H174" s="47">
+        <v>1</v>
+      </c>
+      <c r="I174" s="47"/>
+      <c r="J174" s="47"/>
+      <c r="K174" s="47">
         <f t="shared" si="28"/>
         <v>2</v>
       </c>
@@ -20826,17 +20869,17 @@
       <c r="D175" s="40" t="s">
         <v>380</v>
       </c>
-      <c r="E175" s="61"/>
-      <c r="F175" s="61">
-        <v>1</v>
-      </c>
-      <c r="G175" s="61"/>
-      <c r="H175" s="61">
-        <v>1</v>
-      </c>
-      <c r="I175" s="61"/>
-      <c r="J175" s="61"/>
-      <c r="K175" s="61">
+      <c r="E175" s="47"/>
+      <c r="F175" s="47">
+        <v>1</v>
+      </c>
+      <c r="G175" s="47"/>
+      <c r="H175" s="47">
+        <v>1</v>
+      </c>
+      <c r="I175" s="47"/>
+      <c r="J175" s="47"/>
+      <c r="K175" s="47">
         <f t="shared" si="28"/>
         <v>2</v>
       </c>
@@ -20857,17 +20900,17 @@
       <c r="D176" s="40" t="s">
         <v>381</v>
       </c>
-      <c r="E176" s="61"/>
-      <c r="F176" s="61">
-        <v>1</v>
-      </c>
-      <c r="G176" s="61"/>
-      <c r="H176" s="61">
-        <v>1</v>
-      </c>
-      <c r="I176" s="61"/>
-      <c r="J176" s="61"/>
-      <c r="K176" s="61">
+      <c r="E176" s="47"/>
+      <c r="F176" s="47">
+        <v>1</v>
+      </c>
+      <c r="G176" s="47"/>
+      <c r="H176" s="47">
+        <v>1</v>
+      </c>
+      <c r="I176" s="47"/>
+      <c r="J176" s="47"/>
+      <c r="K176" s="47">
         <f t="shared" si="28"/>
         <v>2</v>
       </c>
@@ -20895,28 +20938,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="58" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="59" t="s">
         <v>391</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="48" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="60" t="s">
         <v>186</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49" t="s">
+      <c r="D2" s="60"/>
+      <c r="E2" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="49"/>
+      <c r="F2" s="61"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -20971,10 +21014,10 @@
       <c r="D5" s="19">
         <v>34</v>
       </c>
-      <c r="E5" s="55" t="s">
+      <c r="E5" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="F5" s="55"/>
+      <c r="F5" s="53"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -21029,20 +21072,20 @@
       <c r="D8" s="19">
         <v>38</v>
       </c>
-      <c r="E8" s="52" t="s">
+      <c r="E8" s="64" t="s">
         <v>233</v>
       </c>
-      <c r="F8" s="52"/>
+      <c r="F8" s="64"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="62" t="s">
         <v>392</v>
       </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="51" t="s">
+      <c r="B9" s="62"/>
+      <c r="C9" s="63" t="s">
         <v>216</v>
       </c>
-      <c r="D9" s="51"/>
+      <c r="D9" s="63"/>
       <c r="E9" s="25" t="s">
         <v>380</v>
       </c>
@@ -21137,10 +21180,10 @@
       <c r="B14" s="22">
         <v>33</v>
       </c>
-      <c r="C14" s="54" t="s">
+      <c r="C14" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="54"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="25" t="s">
         <v>365</v>
       </c>
@@ -21161,10 +21204,10 @@
       <c r="D15" s="28">
         <v>33</v>
       </c>
-      <c r="E15" s="56" t="s">
+      <c r="E15" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="56"/>
+      <c r="F15" s="57"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -21187,10 +21230,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="55" t="s">
         <v>393</v>
       </c>
-      <c r="B17" s="53"/>
+      <c r="B17" s="55"/>
       <c r="C17" s="27" t="s">
         <v>319</v>
       </c>
@@ -21257,10 +21300,10 @@
       <c r="D20" s="28">
         <v>37</v>
       </c>
-      <c r="E20" s="54" t="s">
+      <c r="E20" s="56" t="s">
         <v>394</v>
       </c>
-      <c r="F20" s="54"/>
+      <c r="F20" s="56"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
@@ -21283,14 +21326,14 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="53" t="s">
+      <c r="B22" s="57"/>
+      <c r="C22" s="55" t="s">
         <v>169</v>
       </c>
-      <c r="D22" s="53"/>
+      <c r="D22" s="55"/>
       <c r="E22" s="27" t="s">
         <v>275</v>
       </c>
@@ -21391,16 +21434,16 @@
       <c r="D27" s="14">
         <v>34</v>
       </c>
-      <c r="E27" s="55" t="s">
+      <c r="E27" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="55"/>
+      <c r="F27" s="53"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="57" t="s">
+      <c r="A28" s="52" t="s">
         <v>244</v>
       </c>
-      <c r="B28" s="57"/>
+      <c r="B28" s="52"/>
       <c r="C28" s="13" t="s">
         <v>328</v>
       </c>
@@ -21441,10 +21484,10 @@
       <c r="B30" s="36">
         <v>35</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C30" s="54" t="s">
         <v>395</v>
       </c>
-      <c r="D30" s="58"/>
+      <c r="D30" s="54"/>
       <c r="E30" s="29" t="s">
         <v>262</v>
       </c>
@@ -21538,16 +21581,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -21555,9 +21588,97 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C14:D14"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{270C7FD6-FBAD-4655-8F63-6D8C108A779A}">
+  <dimension ref="K3:L10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="11" max="11" width="13.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="87.7109375" style="39" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K3" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="L3" s="42" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="4" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K4" s="48" t="s">
+        <v>405</v>
+      </c>
+      <c r="L4" s="48" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="5" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K5" s="48" t="s">
+        <v>408</v>
+      </c>
+      <c r="L5" s="48" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K6" s="48" t="s">
+        <v>409</v>
+      </c>
+      <c r="L6" s="48" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K7" s="48" t="s">
+        <v>411</v>
+      </c>
+      <c r="L7" s="48" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K8" s="48" t="s">
+        <v>412</v>
+      </c>
+      <c r="L8" s="48" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="9" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K9" s="48" t="s">
+        <v>413</v>
+      </c>
+      <c r="L9" s="48" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="10" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K10" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>418</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 

--- a/roteiro original.xlsx
+++ b/roteiro original.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC 0025\Desktop\Estudo roteiro promotores  autoserviço\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CC5F88-D2E2-47E4-B29A-D47152014CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AD2BE1-6AD2-419C-A124-DCCAD0DAF80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{18824AD4-335A-446D-A7D9-07F1443FEBAC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{18824AD4-335A-446D-A7D9-07F1443FEBAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -28,19 +28,19 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">rascunho!$A$2:$P$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'roteiro original'!$A$2:$N$133</definedName>
-    <definedName name="_xlcn.WorksheetConnection_AtivmobatualmaioA1O230" hidden="1">[1]promotesativmob!$A$2:$L$134</definedName>
+    <definedName name="_xlcn.WorksheetConnection_AtivmobatualmaioA1O2301" hidden="1">[1]promotesativmob!$A$2:$L$134</definedName>
     <definedName name="SegmentaçãodeDados_Mix_de_produtos_quantidade">#N/A</definedName>
     <definedName name="SegmentaçãodeDados_Promotor">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId10"/>
-    <pivotCache cacheId="9" r:id="rId11"/>
+    <pivotCache cacheId="1" r:id="rId10"/>
+    <pivotCache cacheId="2" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="10" r:id="rId12"/>
+        <pivotCache cacheId="3" r:id="rId12"/>
       </x14:pivotCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -81,7 +81,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Intervalo" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_AtivmobatualmaioA1O230"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_AtivmobatualmaioA1O2301"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -1630,10 +1630,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1661,12 +1667,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4485,7 +4485,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E699402A-8A71-4420-95C9-3464F8567244}" name="Tabela dinâmica1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E699402A-8A71-4420-95C9-3464F8567244}" name="Tabela dinâmica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -4604,7 +4604,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{60B45C95-8E4E-40AD-81AB-1B8E28A41E2F}" name="Tabela dinâmica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{60B45C95-8E4E-40AD-81AB-1B8E28A41E2F}" name="Tabela dinâmica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B102" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -6523,6 +6523,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CECEA20-3F89-4AF0-9A9C-B1A68B340A52}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W133"/>
   <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6546,31 +6547,31 @@
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="G1" s="15">
         <f t="shared" ref="G1:M1" si="0">SUBTOTAL(9,G3:G133)</f>
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="H1" s="15">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="I1" s="15">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="J1" s="15">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="K1" s="15">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="L1" s="15">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="M1" s="15">
         <f t="shared" si="0"/>
-        <v>332</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
@@ -6617,7 +6618,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="40">
         <v>10931</v>
       </c>
@@ -6656,7 +6657,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40">
         <v>10931</v>
       </c>
@@ -6695,7 +6696,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>10931</v>
       </c>
@@ -6732,7 +6733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="40">
         <v>12076</v>
       </c>
@@ -6769,7 +6770,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>10931</v>
       </c>
@@ -6854,7 +6855,7 @@
       <c r="V8" s="39"/>
       <c r="W8" s="39"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="40">
         <v>12076</v>
       </c>
@@ -6891,7 +6892,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="40">
         <v>11023</v>
       </c>
@@ -6930,7 +6931,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="40">
         <v>11678</v>
       </c>
@@ -6969,7 +6970,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26">
         <v>11587</v>
       </c>
@@ -7082,7 +7083,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
         <v>11932</v>
       </c>
@@ -7119,7 +7120,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>11587</v>
       </c>
@@ -7164,7 +7165,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="40">
         <v>11023</v>
       </c>
@@ -7203,7 +7204,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>12028</v>
       </c>
@@ -7240,7 +7241,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>11023</v>
       </c>
@@ -7277,7 +7278,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>12079</v>
       </c>
@@ -7316,7 +7317,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26">
         <v>11023</v>
       </c>
@@ -7353,7 +7354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>11023</v>
       </c>
@@ -7392,7 +7393,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="26">
         <v>11023</v>
       </c>
@@ -7427,7 +7428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>12027</v>
       </c>
@@ -7466,7 +7467,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="26">
         <v>11023</v>
       </c>
@@ -7536,7 +7537,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>12076</v>
       </c>
@@ -7575,7 +7576,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>12087</v>
       </c>
@@ -7614,7 +7615,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26">
         <v>11679</v>
       </c>
@@ -7653,7 +7654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>11679</v>
       </c>
@@ -7690,7 +7691,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>12155</v>
       </c>
@@ -7729,7 +7730,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>11679</v>
       </c>
@@ -7774,7 +7775,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>11678</v>
       </c>
@@ -7813,7 +7814,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>11678</v>
       </c>
@@ -7852,7 +7853,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>11678</v>
       </c>
@@ -7891,7 +7892,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>11678</v>
       </c>
@@ -7930,7 +7931,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <v>12076</v>
       </c>
@@ -7971,7 +7972,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>11678</v>
       </c>
@@ -8054,7 +8055,7 @@
       <c r="V39" s="39"/>
       <c r="W39" s="39"/>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>11932</v>
       </c>
@@ -8093,7 +8094,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:23" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" s="41" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26">
         <v>11678</v>
       </c>
@@ -8139,7 +8140,7 @@
       <c r="V41" s="39"/>
       <c r="W41" s="39"/>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>11868</v>
       </c>
@@ -8261,7 +8262,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="40">
         <v>11868</v>
       </c>
@@ -8300,7 +8301,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="40">
         <v>11868</v>
       </c>
@@ -8378,7 +8379,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
         <v>11932</v>
       </c>
@@ -8417,7 +8418,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="40">
         <v>11868</v>
       </c>
@@ -8502,7 +8503,7 @@
       <c r="V50" s="39"/>
       <c r="W50" s="39"/>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="40">
         <v>10931</v>
       </c>
@@ -8541,7 +8542,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="26">
         <v>11932</v>
       </c>
@@ -8578,7 +8579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="40">
         <v>10931</v>
       </c>
@@ -8661,7 +8662,7 @@
       <c r="V54" s="39"/>
       <c r="W54" s="39"/>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="40">
         <v>12087</v>
       </c>
@@ -8698,7 +8699,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="40">
         <v>12028</v>
       </c>
@@ -8735,7 +8736,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:23" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" s="17" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26">
         <v>11932</v>
       </c>
@@ -8774,7 +8775,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="26">
         <v>11932</v>
       </c>
@@ -8811,7 +8812,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26">
         <v>11932</v>
       </c>
@@ -8846,7 +8847,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="40">
         <v>11587</v>
       </c>
@@ -8961,7 +8962,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="40">
         <v>11956</v>
       </c>
@@ -8998,7 +8999,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="40">
         <v>11956</v>
       </c>
@@ -9037,7 +9038,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="40">
         <v>11956</v>
       </c>
@@ -9082,7 +9083,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="26">
         <v>12028</v>
       </c>
@@ -9117,7 +9118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="40">
         <v>12108</v>
       </c>
@@ -9156,7 +9157,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="40">
         <v>12028</v>
       </c>
@@ -9232,7 +9233,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="40">
         <v>12028</v>
       </c>
@@ -9269,7 +9270,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="26">
         <v>12028</v>
       </c>
@@ -9304,7 +9305,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="40">
         <v>10931</v>
       </c>
@@ -9343,7 +9344,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="40">
         <v>12155</v>
       </c>
@@ -9382,7 +9383,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="40">
         <v>12028</v>
       </c>
@@ -9421,7 +9422,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="26">
         <v>12027</v>
       </c>
@@ -9458,7 +9459,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="40">
         <v>12087</v>
       </c>
@@ -9495,7 +9496,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="40">
         <v>12027</v>
       </c>
@@ -9536,7 +9537,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="40">
         <v>12027</v>
       </c>
@@ -9575,7 +9576,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="40">
         <v>12027</v>
       </c>
@@ -9612,7 +9613,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="40">
         <v>12027</v>
       </c>
@@ -9649,7 +9650,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="40">
         <v>12027</v>
       </c>
@@ -9690,7 +9691,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="40">
         <v>12027</v>
       </c>
@@ -9819,7 +9820,7 @@
       <c r="V84" s="39"/>
       <c r="W84" s="39"/>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="40">
         <v>12079</v>
       </c>
@@ -9858,7 +9859,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="40">
         <v>12079</v>
       </c>
@@ -9897,7 +9898,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="26">
         <v>12079</v>
       </c>
@@ -9932,7 +9933,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="40">
         <v>12079</v>
       </c>
@@ -9971,7 +9972,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="26">
         <v>12079</v>
       </c>
@@ -10052,7 +10053,7 @@
       <c r="V90" s="39"/>
       <c r="W90" s="39"/>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="26">
         <v>12079</v>
       </c>
@@ -10087,7 +10088,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="40">
         <v>11679</v>
       </c>
@@ -10126,7 +10127,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="40">
         <v>12079</v>
       </c>
@@ -10165,7 +10166,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="40">
         <v>12079</v>
       </c>
@@ -10202,7 +10203,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="40">
         <v>12028</v>
       </c>
@@ -10241,7 +10242,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="40">
         <v>12076</v>
       </c>
@@ -10276,7 +10277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="40">
         <v>12082</v>
       </c>
@@ -10313,7 +10314,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="26">
         <v>12076</v>
       </c>
@@ -10350,7 +10351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="26">
         <v>12076</v>
       </c>
@@ -10387,7 +10388,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="40">
         <v>11868</v>
       </c>
@@ -10424,7 +10425,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="40">
         <v>12076</v>
       </c>
@@ -10465,7 +10466,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="40">
         <v>12028</v>
       </c>
@@ -10504,7 +10505,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="40">
         <v>11023</v>
       </c>
@@ -10541,7 +10542,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="40">
         <v>11932</v>
       </c>
@@ -10580,7 +10581,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="40">
         <v>12081</v>
       </c>
@@ -10619,7 +10620,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="40">
         <v>12108</v>
       </c>
@@ -10658,7 +10659,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="26">
         <v>12083</v>
       </c>
@@ -10695,7 +10696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="40">
         <v>12084</v>
       </c>
@@ -10740,7 +10741,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="40">
         <v>12108</v>
       </c>
@@ -10777,7 +10778,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="26">
         <v>12108</v>
       </c>
@@ -10812,7 +10813,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="40">
         <v>12108</v>
       </c>
@@ -10851,7 +10852,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="40">
         <v>12108</v>
       </c>
@@ -10890,7 +10891,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="40">
         <v>11868</v>
       </c>
@@ -10929,7 +10930,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="40">
         <v>12108</v>
       </c>
@@ -11058,7 +11059,7 @@
       <c r="V116" s="39"/>
       <c r="W116" s="39"/>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="26">
         <v>12108</v>
       </c>
@@ -11093,7 +11094,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="40">
         <v>10931</v>
       </c>
@@ -11130,7 +11131,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="40">
         <v>12087</v>
       </c>
@@ -11171,7 +11172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="40">
         <v>11023</v>
       </c>
@@ -11210,7 +11211,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="26">
         <v>12087</v>
       </c>
@@ -11245,7 +11246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="26">
         <v>12087</v>
       </c>
@@ -11280,7 +11281,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:23" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:23" s="41" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="26">
         <v>12087</v>
       </c>
@@ -11326,7 +11327,7 @@
       <c r="V123" s="39"/>
       <c r="W123" s="39"/>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="40">
         <v>12076</v>
       </c>
@@ -11363,7 +11364,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="40">
         <v>12087</v>
       </c>
@@ -11402,7 +11403,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="40">
         <v>12087</v>
       </c>
@@ -11439,7 +11440,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="40">
         <v>12087</v>
       </c>
@@ -11476,7 +11477,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="40">
         <v>11678</v>
       </c>
@@ -11515,7 +11516,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="40">
         <v>11023</v>
       </c>
@@ -11591,7 +11592,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="40">
         <v>12080</v>
       </c>
@@ -11630,7 +11631,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="40">
         <v>12155</v>
       </c>
@@ -11667,7 +11668,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="40">
         <v>12155</v>
       </c>
@@ -11713,7 +11714,31 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N133" xr:uid="{0CECEA20-3F89-4AF0-9A9C-B1A68B340A52}"/>
+  <autoFilter ref="A2:N133" xr:uid="{0CECEA20-3F89-4AF0-9A9C-B1A68B340A52}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="SUPER DO POVO - CAMBEBA"/>
+        <filter val="SUPER DO POVO - CONJUNTO CEARA"/>
+        <filter val="SUPER DO POVO - GUARARAPES"/>
+        <filter val="SUPER DO POVO - HENRIQUE JORGE"/>
+        <filter val="SUPER DO POVO - JUREMA"/>
+        <filter val="SUPER DO POVO - MINI MARKET"/>
+        <filter val="SUPER DO POVO - PARQUE DOIS IRMAOS"/>
+        <filter val="SUPER DO POVO - PASSARE"/>
+        <filter val="SUPER DO POVO - PREF JOSE WALTER"/>
+        <filter val="SUPER LAGOA - CAMBEBA"/>
+        <filter val="SUPER LAGOA - CENTRO"/>
+        <filter val="SUPER LAGOA - CIDADE 2000"/>
+        <filter val="SUPER LAGOA - LUCIANO CAVALCANTE"/>
+        <filter val="SUPER LAGOA - MOZART LUCENA"/>
+        <filter val="SUPER LAGOA - NORTH SHOPPING"/>
+        <filter val="SUPER LAGOA - PARANGABA"/>
+        <filter val="SUPER LAGOA - PASSARE"/>
+        <filter val="SUPER LAGOA - RODOLFO TEOFILO"/>
+        <filter val="SUPER LAGOA - SANTOS DUMONT"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -20885,28 +20910,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="58" t="s">
         <v>388</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="59" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="60" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="59" t="s">
+      <c r="D2" s="60"/>
+      <c r="E2" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="59"/>
+      <c r="F2" s="61"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -20961,10 +20986,10 @@
       <c r="D5" s="19">
         <v>34</v>
       </c>
-      <c r="E5" s="55" t="s">
+      <c r="E5" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="F5" s="55"/>
+      <c r="F5" s="57"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -21019,20 +21044,20 @@
       <c r="D8" s="19">
         <v>38</v>
       </c>
-      <c r="E8" s="62" t="s">
+      <c r="E8" s="64" t="s">
         <v>231</v>
       </c>
-      <c r="F8" s="62"/>
+      <c r="F8" s="64"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="62" t="s">
         <v>390</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="61" t="s">
+      <c r="B9" s="62"/>
+      <c r="C9" s="63" t="s">
         <v>214</v>
       </c>
-      <c r="D9" s="61"/>
+      <c r="D9" s="63"/>
       <c r="E9" s="25" t="s">
         <v>378</v>
       </c>
@@ -21127,10 +21152,10 @@
       <c r="B14" s="22">
         <v>33</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="D14" s="53"/>
+      <c r="D14" s="54"/>
       <c r="E14" s="25" t="s">
         <v>363</v>
       </c>
@@ -21151,10 +21176,10 @@
       <c r="D15" s="28">
         <v>33</v>
       </c>
-      <c r="E15" s="52" t="s">
+      <c r="E15" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="52"/>
+      <c r="F15" s="55"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -21177,10 +21202,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="53" t="s">
         <v>391</v>
       </c>
-      <c r="B17" s="64"/>
+      <c r="B17" s="53"/>
       <c r="C17" s="27" t="s">
         <v>317</v>
       </c>
@@ -21247,10 +21272,10 @@
       <c r="D20" s="28">
         <v>37</v>
       </c>
-      <c r="E20" s="53" t="s">
+      <c r="E20" s="54" t="s">
         <v>392</v>
       </c>
-      <c r="F20" s="53"/>
+      <c r="F20" s="54"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
@@ -21273,14 +21298,14 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="55" t="s">
         <v>203</v>
       </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="64" t="s">
+      <c r="B22" s="55"/>
+      <c r="C22" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="D22" s="64"/>
+      <c r="D22" s="53"/>
       <c r="E22" s="27" t="s">
         <v>273</v>
       </c>
@@ -21381,16 +21406,16 @@
       <c r="D27" s="14">
         <v>34</v>
       </c>
-      <c r="E27" s="55" t="s">
+      <c r="E27" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="55"/>
+      <c r="F27" s="57"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="56" t="s">
         <v>242</v>
       </c>
-      <c r="B28" s="54"/>
+      <c r="B28" s="56"/>
       <c r="C28" s="13" t="s">
         <v>326</v>
       </c>
@@ -21431,10 +21456,10 @@
       <c r="B30" s="36">
         <v>35</v>
       </c>
-      <c r="C30" s="63" t="s">
+      <c r="C30" s="52" t="s">
         <v>393</v>
       </c>
-      <c r="D30" s="63"/>
+      <c r="D30" s="52"/>
       <c r="E30" s="29" t="s">
         <v>260</v>
       </c>
@@ -21528,11 +21553,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="A28:B28"/>
@@ -21545,6 +21565,11 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
